--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,6 +827,1022 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>07:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dalian Yingbo II</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Haimen Codion</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Guangzhou Alpha</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Hubei Istar</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ganzhou Ruishi FC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Guangdong Mingtu</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Guizhou Zhucheng Athletic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Xiamen Feilu</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:08:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.51</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,22 +1389,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1652,13 +1652,13 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 09:08:54</t>
+          <t>2026-06-17 11:19:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1398,7 +1398,7 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,10 +1643,10 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 11:19:19</t>
+          <t>2026-06-17 13:28:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1153,10 +1153,10 @@
         <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1407,16 +1407,16 @@
         <v>1.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
@@ -1661,10 +1661,10 @@
         <v>1.39</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.02</v>
@@ -1842,7 +1842,261 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 13:28:47</t>
+          <t>2026-06-17 15:42:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Lyn</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-17 15:42:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB6"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -905,7 +905,7 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
         <v>1.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
@@ -1652,13 +1652,13 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.12</v>
@@ -1906,10 +1906,10 @@
         <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="R6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -2096,7 +2096,2547 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 15:42:26</t>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X10" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>590</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>330</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Galway Utd</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>St Patricks</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-17 17:51:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB16"/>
+  <dimension ref="A1:CB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1413,11 +1413,11 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.02</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X4" t="n">
         <v>1000</v>
       </c>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,28 +1897,28 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P6" t="n">
         <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.26</v>
@@ -1927,112 +1927,112 @@
         <v>2.22</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH6" t="n">
         <v>7.4</v>
@@ -2044,28 +2044,28 @@
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>2.36</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BN6" t="n">
         <v>7.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP6" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BR6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS6" t="n">
         <v>2.6</v>
@@ -2074,19 +2074,19 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>2.36</v>
       </c>
       <c r="BV6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BX6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,226 +2118,226 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW7" t="n">
         <v>1.68</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
         <v>1.75</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.76</v>
+        <v>5.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.89</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>1.58</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>1.68</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>2.46</v>
       </c>
       <c r="W8" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH8" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AI8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BT8" t="n">
         <v>4.5</v>
       </c>
-      <c r="BO8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BU8" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K9" t="n">
         <v>6.8</v>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG9" t="n">
         <v>12</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AH9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>280</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>32</v>
       </c>
-      <c r="AE9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AR9" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>6.8</v>
       </c>
       <c r="AU9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD9" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BE9" t="n">
-        <v>3.95</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BP9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>11</v>
-      </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.4</v>
+        <v>1.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.1</v>
+        <v>1.86</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>1.37</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>2.58</v>
       </c>
       <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>590</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BE10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="BK10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP10" t="n">
         <v>38</v>
       </c>
-      <c r="AI10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>330</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="BT10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.6</v>
+        <v>3.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY10" t="n">
-        <v>9.4</v>
+        <v>3.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.42</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>1.37</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="Z11" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>590</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>250</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
         <v>48</v>
       </c>
-      <c r="AK11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>330</v>
       </c>
       <c r="AP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
         <v>10</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS11" t="n">
+      <c r="AV11" t="n">
         <v>4</v>
       </c>
-      <c r="AT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AW11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BA11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
         <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.38</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>40</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.24</v>
+        <v>7.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.36</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.84</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,229 +3388,229 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.05</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
-        <v>2.36</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="Z12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
         <v>16.5</v>
       </c>
-      <c r="AA12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>3.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK12" t="n">
         <v>5.4</v>
       </c>
-      <c r="BD12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>2.74</v>
-      </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>3.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="H13" t="n">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X13" t="n">
         <v>17</v>
       </c>
-      <c r="J13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>23</v>
       </c>
-      <c r="Y13" t="n">
-        <v>950</v>
-      </c>
       <c r="Z13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA13" t="n">
         <v>150</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
       <c r="AB13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
-        <v>310</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AZ13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>23</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.02</v>
+        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.9</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>1.84</v>
       </c>
       <c r="H14" t="n">
-        <v>1.58</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.68</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX14" t="n">
         <v>4.1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="AY14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>4.7</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="BA14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
         <v>1.78</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X14" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>5.6</v>
       </c>
-      <c r="BF14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BR14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>1.69</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="BV14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>1.74</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>1.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,229 +4150,229 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO15" t="n">
         <v>4.2</v>
       </c>
-      <c r="G15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X15" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>7</v>
       </c>
-      <c r="AV15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="BT15" t="n">
         <v>6.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="BX15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>
@@ -4431,25 +4431,25 @@
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>2.72</v>
@@ -4542,7 +4542,7 @@
         <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH16" t="n">
         <v>5.3</v>
@@ -4584,13 +4584,13 @@
         <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BN16" t="n">
         <v>6.8</v>
@@ -4602,13 +4602,13 @@
         <v>19</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
@@ -4620,13 +4620,13 @@
         <v>46</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,515 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 17:51:34</t>
+          <t>2026-06-17 20:00:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-17 20:00:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CSD Liniers de Ciudad Evita</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-17 20:00:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1219,52 +1219,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1276,65 +1276,65 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1473,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1727,52 +1727,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>44</v>
       </c>
       <c r="Y6" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
         <v>55</v>
@@ -1981,16 +1981,16 @@
         <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>12</v>
@@ -2002,7 +2002,7 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -2014,7 +2014,7 @@
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
@@ -2026,7 +2026,7 @@
         <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
         <v>5.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         <v>19</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
         <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -3287,7 +3287,7 @@
         <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
         <v>10.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
         <v>4.8</v>
@@ -3956,7 +3956,7 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
         <v>2.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4694,7 +4694,7 @@
         <v>2.78</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17" t="n">
         <v>1.58</v>
@@ -4715,11 +4715,11 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.47</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X17" t="n">
         <v>1000</v>
       </c>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5029,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -5086,65 +5086,65 @@
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 20:00:52</t>
+          <t>2026-06-17 22:10:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,16 +1389,16 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         <v>12.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.36</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,7 +2056,7 @@
         <v>7.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BP6" t="n">
         <v>15.5</v>
@@ -2074,7 +2074,7 @@
         <v>12.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>2.36</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
         <v>42</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.81</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
         <v>1.07</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="H11" t="n">
         <v>11</v>
@@ -3188,13 +3188,13 @@
         <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X11" t="n">
         <v>29</v>
@@ -3209,7 +3209,7 @@
         <v>590</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>16.5</v>
@@ -3224,7 +3224,7 @@
         <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>38</v>
@@ -3236,10 +3236,10 @@
         <v>12.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>210</v>
@@ -3254,13 +3254,13 @@
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.8</v>
@@ -3269,10 +3269,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3281,10 +3281,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB11" t="n">
         <v>7.6</v>
@@ -3293,16 +3293,16 @@
         <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
         <v>3.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
         <v>3.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3840,7 +3840,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3852,7 +3852,7 @@
         <v>8.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
         <v>1.73</v>
@@ -3944,7 +3944,7 @@
         <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
         <v>1.79</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>4.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -4321,58 +4321,58 @@
         <v>3.85</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
         <v>3.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
         <v>2.7</v>
@@ -4584,13 +4584,13 @@
         <v>13</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.98</v>
+        <v>1.91</v>
       </c>
       <c r="BN16" t="n">
         <v>6.8</v>
@@ -4602,13 +4602,13 @@
         <v>19</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.58</v>
+        <v>1.74</v>
       </c>
       <c r="BR16" t="n">
         <v>34</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.74</v>
+        <v>1.81</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
@@ -4620,13 +4620,13 @@
         <v>46</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-17 22:10:20</t>
+          <t>2026-06-18 00:19:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,13 +1389,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,196 +1897,196 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.74</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>2.12</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="BP6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>2.12</v>
       </c>
       <c r="BV6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2127,220 +2127,220 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.15</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.81</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="BN7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>1.47</v>
       </c>
       <c r="BP7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.2</v>
+        <v>1.37</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BX7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>1.58</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H9" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.05</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="W9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
         <v>1.74</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
         <v>1.83</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -2889,220 +2889,220 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="BN10" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="BP10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="BT10" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="BV10" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="BX10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="G11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>1.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3397,220 +3397,220 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>1.13</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3651,220 +3651,220 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>10.5</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
         <v>1.27</v>
@@ -3941,184 +3941,184 @@
         <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="G15" t="n">
         <v>2.76</v>
@@ -4168,13 +4168,13 @@
         <v>2.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.31</v>
@@ -4183,7 +4183,7 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
@@ -4207,118 +4207,118 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W15" t="n">
         <v>1.57</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4413,220 +4413,220 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
         <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="BR16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="BT16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.9</v>
+        <v>1.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
         <v>1.02</v>
@@ -4700,13 +4700,13 @@
         <v>1.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4829,7 +4829,7 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BI17" t="n">
         <v>2.14</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 00:19:35</t>
+          <t>2026-06-18 02:28:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -1876,10 +1876,10 @@
         <v>1.65</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>5.7</v>
@@ -1888,7 +1888,7 @@
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1909,10 +1909,10 @@
         <v>1.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1924,7 +1924,7 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2136,10 +2136,10 @@
         <v>1.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,16 +2151,16 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W7" t="n">
         <v>1.26</v>
@@ -2298,19 +2298,19 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,7 +2328,7 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
@@ -2390,10 +2390,10 @@
         <v>1.58</v>
       </c>
       <c r="I8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
         <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
         <v>1.7</v>
@@ -2420,19 +2420,19 @@
         <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2638,19 +2638,19 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,34 +2659,34 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.26</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.11</v>
       </c>
       <c r="U9" t="n">
         <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2806,7 +2806,7 @@
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -2898,19 +2898,19 @@
         <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
         <v>3.2</v>
@@ -2919,7 +2919,7 @@
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.14</v>
       </c>
       <c r="O11" t="n">
         <v>1.19</v>
@@ -3185,7 +3185,7 @@
         <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="U11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>8.4</v>
@@ -3412,7 +3412,7 @@
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
@@ -3442,13 +3442,13 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.61</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O13" t="n">
         <v>1.29</v>
@@ -3684,7 +3684,7 @@
         <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -3702,7 +3702,7 @@
         <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3956,7 +3956,7 @@
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4180,10 +4180,10 @@
         <v>1.31</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
         <v>4.6</v>
@@ -4428,7 +4428,7 @@
         <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,7 +4437,7 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
@@ -4446,7 +4446,7 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
         <v>1.43</v>
@@ -4464,7 +4464,7 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="H17" t="n">
         <v>2.04</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4703,10 +4703,10 @@
         <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 02:28:43</t>
+          <t>2026-06-18 04:37:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q5" t="n">
         <v>1.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2127,166 +2127,166 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I7" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.15</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.94</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.84</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,13 +2328,13 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.76</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2638,227 +2638,227 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
         <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
         <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.68</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.83</v>
+        <v>9.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.83</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.65</v>
+        <v>5.5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -2889,220 +2889,220 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
         <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J10" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>2.42</v>
+        <v>7.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.76</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2.72</v>
+        <v>7.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.68</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.72</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.14</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3397,166 +3397,166 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="H13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.13</v>
@@ -3675,7 +3675,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
         <v>1.29</v>
@@ -3684,7 +3684,7 @@
         <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -3693,16 +3693,16 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -3905,166 +3905,166 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE14" t="n">
         <v>2.1</v>
       </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4112,13 +4112,13 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4159,220 +4159,220 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
         <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.4</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
         <v>1.57</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4413,166 +4413,166 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,7 +4584,7 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4602,7 +4602,7 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,7 +4614,7 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -4667,166 +4667,166 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="G17" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="H17" t="n">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP17" t="n">
         <v>3.25</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH17" t="n">
         <v>3.65</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 04:37:53</t>
+          <t>2026-06-18 06:47:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB18"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.22</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.02</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.57</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1365,112 +1365,112 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>1.22</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
         <v>1.01</v>
@@ -1527,68 +1527,68 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.53</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
@@ -1903,31 +1903,31 @@
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S6" t="n">
         <v>2.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1936,37 +1936,37 @@
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD6" t="n">
         <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
         <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1975,22 +1975,22 @@
         <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
         <v>12</v>
@@ -1999,40 +1999,40 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
         <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH6" t="n">
         <v>5.3</v>
@@ -2044,7 +2044,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2053,10 +2053,10 @@
         <v>11.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP6" t="n">
         <v>10.5</v>
@@ -2068,25 +2068,25 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="n">
         <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.15</v>
@@ -2169,7 +2169,7 @@
         <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
         <v>2.04</v>
@@ -2178,7 +2178,7 @@
         <v>1.94</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -2193,7 +2193,7 @@
         <v>25</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8.6</v>
@@ -2208,7 +2208,7 @@
         <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>20</v>
@@ -2223,13 +2223,13 @@
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
         <v>16.5</v>
@@ -2259,7 +2259,7 @@
         <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
         <v>14.5</v>
@@ -2268,19 +2268,19 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
         <v>44</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,7 +2328,7 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
         <v>6.8</v>
@@ -2420,10 +2420,10 @@
         <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
         <v>2.1</v>
@@ -2468,16 +2468,16 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
         <v>180</v>
       </c>
       <c r="AK8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AL8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
         <v>120</v>
@@ -2513,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY8" t="n">
         <v>20</v>
@@ -2525,19 +2525,19 @@
         <v>4.4</v>
       </c>
       <c r="BB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG8" t="n">
         <v>6.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I9" t="n">
         <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="n">
         <v>6.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2662,13 +2662,13 @@
         <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
         <v>1.5</v>
@@ -2677,16 +2677,16 @@
         <v>2.82</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
         <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X9" t="n">
         <v>24</v>
@@ -2704,7 +2704,7 @@
         <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD9" t="n">
         <v>950</v>
@@ -2716,7 +2716,7 @@
         <v>7.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>950</v>
@@ -2737,7 +2737,7 @@
         <v>260</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO9" t="n">
         <v>420</v>
@@ -2746,25 +2746,25 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>11.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
@@ -2773,13 +2773,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC9" t="n">
         <v>13</v>
@@ -2788,19 +2788,19 @@
         <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH9" t="n">
         <v>4.3</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ9" t="n">
         <v>14.5</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,226 +2880,226 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL10" t="n">
         <v>50</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>55</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE10" t="n">
         <v>5.2</v>
       </c>
-      <c r="BD10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF10" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
         <v>8</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.29</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="S11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB11" t="n">
         <v>14</v>
       </c>
-      <c r="J11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X11" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>46</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>15.5</v>
+        <v>48</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.2</v>
+        <v>48</v>
       </c>
       <c r="AO11" t="n">
-        <v>330</v>
+        <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY11" t="n">
         <v>8</v>
       </c>
-      <c r="AS11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
         <v>5.6</v>
@@ -3415,7 +3415,7 @@
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3448,58 +3448,58 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
         <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
         <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AO12" t="n">
         <v>120</v>
@@ -3511,10 +3511,10 @@
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3526,19 +3526,19 @@
         <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3547,16 +3547,16 @@
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
         <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -3672,145 +3672,145 @@
         <v>1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -3908,16 +3908,16 @@
         <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
@@ -3935,7 +3935,7 @@
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.81</v>
@@ -3950,13 +3950,13 @@
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3965,16 +3965,16 @@
         <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -4001,28 +4001,28 @@
         <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
         <v>95</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.93</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -4031,40 +4031,40 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8</v>
-      </c>
       <c r="BG14" t="n">
-        <v>2.08</v>
+        <v>5.3</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>1.36</v>
       </c>
       <c r="H15" t="n">
-        <v>2.82</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="K15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W15" t="n">
         <v>3.8</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.57</v>
-      </c>
       <c r="X15" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>530</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE15" t="n">
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>11</v>
+      </c>
+      <c r="CA15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0</v>
-      </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,175 +4404,175 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Fjolnir</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Hviti Riddarinn</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.05</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,13 +4584,13 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
@@ -4602,19 +4602,19 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
@@ -4629,21 +4629,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,498 +4653,1768 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>KH Hlidarendi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>UMF Tindstoll</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 06:47:11</t>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Icelandic 2 Deild</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Throttur Vogar</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kari</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Vidir Gardur</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Reynir Sandgeroi</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Icelandic 3 Deild</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>KA Asvellir</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FC Arbaer</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Miramar Misiones</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Huracan del Paso</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CA Ituzaingo</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F23" t="n">
         <v>1.09</v>
       </c>
-      <c r="G18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
         <v>1.09</v>
       </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.09</v>
       </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
         <v>1.25</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="O23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.12</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S23" t="n">
         <v>1.05</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T23" t="n">
         <v>1.11</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U23" t="n">
         <v>1.11</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V23" t="n">
         <v>1.02</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W23" t="n">
         <v>1.02</v>
       </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>2026-06-18 06:47:11</t>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-18 08:58:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,67 +860,67 @@
         <v>3.6</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.51</v>
       </c>
-      <c r="M2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.55</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
@@ -929,19 +929,19 @@
         <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>80</v>
@@ -953,106 +953,106 @@
         <v>85</v>
       </c>
       <c r="AL2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN2" t="n">
         <v>110</v>
       </c>
-      <c r="AM2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>120</v>
-      </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AW2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BN2" t="n">
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
@@ -1061,26 +1061,26 @@
         <v>3.55</v>
       </c>
       <c r="BV2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>3.75</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="J3" t="n">
         <v>2.78</v>
@@ -1129,7 +1129,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -1159,7 +1159,7 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
         <v>1.86</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1365,184 +1365,184 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="n">
         <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
         <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>1.06</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
         <v>1.56</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
         <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
         <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
@@ -1554,41 +1554,41 @@
         <v>24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV4" t="n">
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -1637,7 +1637,7 @@
         <v>7.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1646,19 +1646,19 @@
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
         <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
@@ -1903,7 +1903,7 @@
         <v>1.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q6" t="n">
         <v>1.4</v>
@@ -1924,7 +1924,7 @@
         <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
         <v>44</v>
@@ -1963,7 +1963,7 @@
         <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
@@ -1981,7 +1981,7 @@
         <v>36</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
@@ -1999,10 +1999,10 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2023,10 +2023,10 @@
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
         <v>5.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
         <v>2.06</v>
@@ -2160,19 +2160,19 @@
         <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
         <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>1.94</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,19 +2328,19 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I8" t="n">
         <v>1.68</v>
@@ -2432,7 +2432,7 @@
         <v>2.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -2626,239 +2626,239 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="S9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB9" t="n">
         <v>13.5</v>
       </c>
-      <c r="I9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="AC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
         <v>6.6</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>300</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="AV9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5.4</v>
       </c>
-      <c r="AO9" t="n">
-        <v>420</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="BD9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BT9" t="n">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
@@ -2922,7 +2922,7 @@
         <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
@@ -2931,7 +2931,7 @@
         <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
         <v>2.08</v>
@@ -2940,7 +2940,7 @@
         <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
@@ -2964,13 +2964,13 @@
         <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>970</v>
@@ -2979,22 +2979,22 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
         <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -3018,43 +3018,43 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.8</v>
       </c>
       <c r="BH10" t="n">
         <v>3.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ10" t="n">
         <v>13.5</v>
@@ -3093,7 +3093,7 @@
         <v>4.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
         <v>7.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>300</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>420</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BO11" t="n">
         <v>3.15</v>
       </c>
-      <c r="G11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BP11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>12</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="CA11" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>0</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R12" t="n">
         <v>1.41</v>
@@ -3511,7 +3511,7 @@
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
         <v>4.2</v>
@@ -3520,7 +3520,7 @@
         <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>16.5</v>
@@ -3532,7 +3532,7 @@
         <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -3681,28 +3681,28 @@
         <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
@@ -3846,7 +3846,7 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7</v>
+        <v>1.33</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.8</v>
+        <v>1.33</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>1.33</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
         <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
@@ -3962,7 +3962,7 @@
         <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="n">
         <v>55</v>
@@ -3977,7 +3977,7 @@
         <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>85</v>
@@ -4007,34 +4007,34 @@
         <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AO14" t="n">
         <v>95</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS14" t="n">
         <v>5</v>
       </c>
-      <c r="AS14" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AU14" t="n">
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4043,28 +4043,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
         <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4082,7 +4082,7 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
@@ -4094,7 +4094,7 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
@@ -4112,13 +4112,13 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4198,13 +4198,13 @@
         <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
         <v>1.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -4228,7 +4228,7 @@
         <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD15" t="n">
         <v>55</v>
@@ -4243,13 +4243,13 @@
         <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
         <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>17.5</v>
@@ -4261,7 +4261,7 @@
         <v>180</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO15" t="n">
         <v>280</v>
@@ -4270,25 +4270,25 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>3.95</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4297,10 +4297,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,16 +4309,16 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="n">
         <v>4.7</v>
@@ -4348,7 +4348,7 @@
         <v>7.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
         <v>23</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.06</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
         <v>1.05</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
         <v>2.02</v>
@@ -4930,7 +4930,7 @@
         <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.9</v>
@@ -4954,19 +4954,19 @@
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
@@ -4975,7 +4975,7 @@
         <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
         <v>22</v>
@@ -4990,7 +4990,7 @@
         <v>13.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
         <v>20</v>
@@ -4999,10 +4999,10 @@
         <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
         <v>21</v>
@@ -5011,7 +5011,7 @@
         <v>60</v>
       </c>
       <c r="AJ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
@@ -5035,10 +5035,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>9.6</v>
@@ -5071,16 +5071,16 @@
         <v>14</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
         <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="n">
         <v>1000</v>
@@ -5092,7 +5092,7 @@
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5116,19 +5116,19 @@
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,127 +5166,127 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>1.07</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>1.01</v>
@@ -5295,13 +5295,13 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
         <v>1.01</v>
@@ -5310,102 +5310,102 @@
         <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic 3 Deild</t>
+          <t>Icelandic 2 Deild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vidir Gardur</t>
+          <t>Throttur Vogar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reynir Sandgeroi</t>
+          <t>Kari</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.07</v>
@@ -5468,13 +5468,13 @@
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5594,65 +5594,65 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
@@ -5674,31 +5674,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KA Asvellir</t>
+          <t>Vidir Gardur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arbaer</t>
+          <t>Reynir Sandgeroi</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
         <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -5710,19 +5710,19 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="P21" t="n">
         <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Icelandic 3 Deild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,251 +5923,251 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>KA Asvellir</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Huracan del Paso</t>
+          <t>FC Arbaer</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.56</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>1.26</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 08:58:41</t>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,60 +6177,60 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>2.54</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="H23" t="n">
-        <v>1.09</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
-        <v>1.09</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
         <v>1.11</v>
@@ -6239,182 +6239,436 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:11:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CA Ituzaingo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CSD Liniers de Ciudad Evita</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.02</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>1.02</v>
       </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-06-18 08:58:41</t>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:11:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
@@ -869,13 +869,13 @@
         <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -887,16 +887,16 @@
         <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -944,13 +944,13 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
         <v>100</v>
@@ -986,22 +986,22 @@
         <v>5.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
         <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>8</v>
@@ -1013,7 +1013,7 @@
         <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
         <v>7.2</v>
@@ -1022,7 +1022,7 @@
         <v>2.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1043,7 +1043,7 @@
         <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
         <v>2.14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.75</v>
       </c>
-      <c r="I3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
         <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
         <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1368,19 +1368,19 @@
         <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.48</v>
@@ -1392,7 +1392,7 @@
         <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P4" t="n">
         <v>1.52</v>
@@ -1401,40 +1401,40 @@
         <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
         <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
         <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
@@ -1443,10 +1443,10 @@
         <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>28</v>
@@ -1473,64 +1473,64 @@
         <v>90</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.15</v>
+        <v>1.54</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.75</v>
+        <v>1.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>1.54</v>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>1.32</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.9</v>
+        <v>1.54</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.55</v>
+        <v>1.42</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.1</v>
+        <v>1.51</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.55</v>
+        <v>1.54</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.4</v>
+        <v>1.54</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.8</v>
+        <v>1.46</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>1.49</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.1</v>
+        <v>1.51</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
         <v>2.8</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1781,68 +1781,68 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -1876,58 +1876,58 @@
         <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="S6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U6" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1939,10 +1939,10 @@
         <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
         <v>24</v>
@@ -1960,28 +1960,28 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
         <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
@@ -1990,16 +1990,16 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
         <v>4</v>
@@ -2017,76 +2017,76 @@
         <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC6" t="n">
         <v>11.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
         <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>3.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN6" t="n">
         <v>5.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
         <v>4.5</v>
@@ -2136,10 +2136,10 @@
         <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.75</v>
@@ -2157,64 +2157,64 @@
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
       <c r="AE7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH7" t="n">
         <v>23</v>
       </c>
-      <c r="AF7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>120</v>
@@ -2223,16 +2223,16 @@
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
         <v>11.5</v>
@@ -2244,49 +2244,49 @@
         <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
         <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="AY7" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>3.35</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>44</v>
+        <v>3.45</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2334,13 +2334,13 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
         <v>1.62</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.61</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2381,55 +2381,55 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
         <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="W8" t="n">
         <v>1.19</v>
@@ -2444,142 +2444,142 @@
         <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL8" t="n">
         <v>85</v>
       </c>
-      <c r="AL8" t="n">
-        <v>80</v>
-      </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>2.22</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>2.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>2.42</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>2.76</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.199999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>2.76</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>2.76</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>2.52</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>2.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>2.68</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>2.78</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="BG8" t="n">
         <v>6.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>1.95</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>2.34</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BP8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ8" t="n">
-        <v>8.6</v>
+        <v>2.28</v>
       </c>
       <c r="BR8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BU8" t="n">
         <v>3.5</v>
@@ -2588,23 +2588,23 @@
         <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.3</v>
+        <v>1.97</v>
       </c>
       <c r="BX8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>7.2</v>
+        <v>2.22</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>6.4</v>
+        <v>2.16</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2635,34 +2635,34 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
         <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
         <v>1.78</v>
@@ -2671,130 +2671,130 @@
         <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>1.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.2</v>
+        <v>1.33</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>1.33</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>1.33</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>1.33</v>
       </c>
       <c r="BA9" t="n">
-        <v>34</v>
+        <v>1.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.6</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.4</v>
+        <v>1.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.8</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>1.33</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.78</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.8</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2904,37 +2904,37 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
@@ -2943,31 +2943,31 @@
         <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
@@ -2976,133 +2976,133 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
         <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.86</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>1.84</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.9</v>
+        <v>2.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>2.04</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>1.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>2.14</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BJ10" t="n">
         <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.4</v>
+        <v>1.81</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>1.47</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.8</v>
+        <v>1.71</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.8</v>
+        <v>1.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>1.72</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
         <v>1.32</v>
@@ -3155,37 +3155,37 @@
         <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="K11" t="n">
         <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
         <v>1.69</v>
@@ -3203,7 +3203,7 @@
         <v>950</v>
       </c>
       <c r="Z11" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -3215,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE11" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AF11" t="n">
         <v>7.6</v>
@@ -3230,103 +3230,103 @@
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AN11" t="n">
         <v>5.8</v>
       </c>
       <c r="AO11" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV11" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
         <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
@@ -3335,38 +3335,38 @@
         <v>6</v>
       </c>
       <c r="BR11" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>2.06</v>
       </c>
       <c r="BT11" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.6</v>
+        <v>2.18</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.6</v>
+        <v>2.18</v>
       </c>
       <c r="BZ11" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.5</v>
+        <v>1.92</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>1.28</v>
@@ -3445,10 +3445,10 @@
         <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3472,7 +3472,7 @@
         <v>28</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
         <v>12.5</v>
@@ -3487,16 +3487,16 @@
         <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
         <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
         <v>10.5</v>
@@ -3505,28 +3505,28 @@
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>2.54</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>2.62</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3538,7 +3538,7 @@
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3547,16 +3547,16 @@
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>2.26</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>2.82</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
         <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>5.8</v>
@@ -3666,34 +3666,34 @@
         <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
         <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
         <v>1.98</v>
@@ -3705,7 +3705,7 @@
         <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -3714,31 +3714,31 @@
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF13" t="n">
         <v>11</v>
       </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>25</v>
@@ -3750,70 +3750,70 @@
         <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.46</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.58</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AV13" t="n">
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.44</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG13" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
         <v>1.04</v>
@@ -3822,49 +3822,49 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -3905,85 +3905,85 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
         <v>970</v>
       </c>
-      <c r="Y14" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,7 +3992,7 @@
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
         <v>970</v>
@@ -4004,67 +4004,67 @@
         <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
         <v>970</v>
       </c>
       <c r="AO14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>2.64</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.45</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G15" t="n">
         <v>1.36</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="J15" t="n">
         <v>5.7</v>
@@ -4207,10 +4207,10 @@
         <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
@@ -4237,7 +4237,7 @@
         <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
@@ -4270,25 +4270,25 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,22 +4309,22 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
         <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="n">
         <v>4.7</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ15" t="n">
         <v>12.5</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -4703,16 +4703,16 @@
         <v>1.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="S17" t="n">
         <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
         <v>2.02</v>
@@ -4936,10 +4936,10 @@
         <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4948,19 +4948,19 @@
         <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
         <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.66</v>
@@ -4969,172 +4969,172 @@
         <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
         <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
         <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
         <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>2.42</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>2.42</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>36</v>
+        <v>2.42</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AZ18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP18" t="n">
         <v>14</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BQ18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX18" t="n">
         <v>38</v>
       </c>
-      <c r="BB18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
         <v>1.58</v>
@@ -5187,37 +5187,37 @@
         <v>7.4</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S19" t="n">
         <v>2.28</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
@@ -5241,13 +5241,13 @@
         <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AE19" t="n">
         <v>90</v>
@@ -5259,7 +5259,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
         <v>80</v>
@@ -5268,13 +5268,13 @@
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
         <v>6.8</v>
@@ -5295,7 +5295,7 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
         <v>8.800000000000001</v>
@@ -5307,13 +5307,13 @@
         <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5331,19 +5331,19 @@
         <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
         <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
@@ -5355,13 +5355,13 @@
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.01</v>
@@ -5373,7 +5373,7 @@
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU19" t="n">
         <v>1.01</v>
@@ -5391,14 +5391,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
         <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5456,7 +5456,7 @@
         <v>1.26</v>
       </c>
       <c r="O20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P20" t="n">
         <v>1.25</v>
@@ -5468,7 +5468,7 @@
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5707,28 +5707,28 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P21" t="n">
         <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="R22" t="n">
         <v>1.24</v>
@@ -5979,10 +5979,10 @@
         <v>1.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
         <v>2.92</v>
@@ -6203,40 +6203,40 @@
         <v>3.05</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
@@ -6245,10 +6245,10 @@
         <v>1.52</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
         <v>23</v>
@@ -6257,10 +6257,10 @@
         <v>55</v>
       </c>
       <c r="AB23" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD23" t="n">
         <v>15.5</v>
@@ -6308,7 +6308,7 @@
         <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -6326,25 +6326,25 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF23" t="n">
         <v>19.5</v>
@@ -6353,68 +6353,68 @@
         <v>21</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 11:11:50</t>
+          <t>2026-06-18 13:25:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -866,16 +866,16 @@
         <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -887,16 +887,16 @@
         <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -905,7 +905,7 @@
         <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
@@ -968,7 +968,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
         <v>5.5</v>
@@ -980,7 +980,7 @@
         <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV2" t="n">
         <v>5.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
         <v>1.21</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
@@ -1165,7 +1165,7 @@
         <v>1.86</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
         <v>15.5</v>
@@ -1201,7 +1201,7 @@
         <v>110</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>30</v>
@@ -1225,88 +1225,88 @@
         <v>3.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
         <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
         <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>4.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP3" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BT3" t="n">
         <v>8.4</v>
@@ -1324,17 +1324,17 @@
         <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BZ3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
@@ -1389,7 +1389,7 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O4" t="n">
         <v>1.52</v>
@@ -1404,7 +1404,7 @@
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>1.06</v>
       </c>
       <c r="T4" t="n">
         <v>2.06</v>
@@ -1413,7 +1413,7 @@
         <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
         <v>1.57</v>
@@ -1479,7 +1479,7 @@
         <v>1.54</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS4" t="n">
         <v>1.54</v>
@@ -1503,7 +1503,7 @@
         <v>1.54</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BA4" t="n">
         <v>1.52</v>
@@ -1512,13 +1512,13 @@
         <v>1.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BF4" t="n">
         <v>1.5</v>
@@ -1530,7 +1530,7 @@
         <v>2.78</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -1655,10 +1655,10 @@
         <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1781,28 +1781,28 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.92</v>
+        <v>1.83</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.23</v>
@@ -1906,13 +1906,13 @@
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
         <v>1.81</v>
       </c>
       <c r="S6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
         <v>1.52</v>
@@ -1924,7 +1924,7 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
         <v>42</v>
@@ -1939,7 +1939,7 @@
         <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
@@ -1951,7 +1951,7 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>13.5</v>
@@ -1960,7 +1960,7 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
         <v>23</v>
@@ -1969,28 +1969,28 @@
         <v>19</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO6" t="n">
         <v>38</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
@@ -1999,10 +1999,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>3.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2014,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
         <v>13.5</v>
@@ -2026,19 +2026,19 @@
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
         <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="n">
         <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="G7" t="n">
         <v>4.5</v>
@@ -2136,16 +2136,16 @@
         <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2175,118 +2175,118 @@
         <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>1.09</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>1.09</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="AS7" t="n">
-        <v>18</v>
+        <v>1.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>1.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>14.5</v>
+        <v>1.09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>1.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>1.09</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2298,19 +2298,19 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2328,19 +2328,19 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
         <v>1.75</v>
@@ -2423,10 +2423,10 @@
         <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
         <v>2.42</v>
@@ -2438,10 +2438,10 @@
         <v>22</v>
       </c>
       <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
         <v>11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12</v>
       </c>
       <c r="AA8" t="n">
         <v>19.5</v>
@@ -2450,13 +2450,13 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
         <v>55</v>
@@ -2465,7 +2465,7 @@
         <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>38</v>
@@ -2492,119 +2492,119 @@
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.76</v>
+        <v>3.55</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>2.54</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="BN8" t="n">
         <v>12.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BP8" t="n">
         <v>48</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BV8" t="n">
         <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8" t="n">
         <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2641,16 +2641,16 @@
         <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
@@ -2665,7 +2665,7 @@
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
         <v>2.04</v>
@@ -2677,13 +2677,13 @@
         <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
         <v>1.42</v>
@@ -2746,7 +2746,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
         <v>1.23</v>
@@ -2755,7 +2755,7 @@
         <v>1.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>1.33</v>
@@ -2770,7 +2770,7 @@
         <v>1.33</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.33</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>1.33</v>
@@ -2794,13 +2794,13 @@
         <v>1.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.33</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="n">
         <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
         <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
         <v>970</v>
@@ -2985,7 +2985,7 @@
         <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2997,28 +2997,28 @@
         <v>40</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AR10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW10" t="n">
         <v>2.14</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.04</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
@@ -3027,13 +3027,13 @@
         <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -3042,13 +3042,13 @@
         <v>2.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
         <v>13.5</v>
@@ -3155,46 +3155,46 @@
         <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
         <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -3209,28 +3209,28 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC11" t="n">
         <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>330</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
@@ -3242,13 +3242,13 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
         <v>5.8</v>
       </c>
       <c r="AO11" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AP11" t="n">
         <v>17.5</v>
@@ -3257,10 +3257,10 @@
         <v>32</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3269,10 +3269,10 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3281,13 +3281,13 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
@@ -3296,16 +3296,16 @@
         <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI11" t="n">
         <v>3.6</v>
@@ -3314,59 +3314,59 @@
         <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.96</v>
+        <v>10.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="BN11" t="n">
         <v>4.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="BP11" t="n">
         <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="BT11" t="n">
         <v>23</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>15.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.92</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3400,10 @@
         <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>8</v>
@@ -3412,10 +3412,10 @@
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3442,7 +3442,7 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.14</v>
@@ -3454,7 +3454,7 @@
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z12" t="n">
         <v>65</v>
@@ -3466,22 +3466,22 @@
         <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>95</v>
@@ -3505,40 +3505,40 @@
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.28</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.62</v>
+        <v>19.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
         <v>11.5</v>
@@ -3547,70 +3547,70 @@
         <v>12</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.26</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
         <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>5.8</v>
@@ -3666,37 +3666,37 @@
         <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.21</v>
@@ -3705,7 +3705,7 @@
         <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
         <v>24</v>
@@ -3714,31 +3714,31 @@
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
         <v>25</v>
@@ -3750,16 +3750,16 @@
         <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>2.52</v>
       </c>
       <c r="AQ13" t="n">
         <v>12</v>
@@ -3768,103 +3768,103 @@
         <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>2.52</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>2.52</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>2.52</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.4</v>
+        <v>1.9</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
         <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3929,7 +3929,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>1.98</v>
       </c>
       <c r="O14" t="n">
         <v>1.27</v>
@@ -3938,7 +3938,7 @@
         <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -3950,10 +3950,10 @@
         <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>2.2</v>
@@ -4013,16 +4013,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
@@ -4034,10 +4034,10 @@
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AY14" t="n">
         <v>6.6</v>
@@ -4046,25 +4046,25 @@
         <v>2.36</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H15" t="n">
         <v>10.5</v>
@@ -4198,7 +4198,7 @@
         <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
         <v>1.98</v>
@@ -4210,7 +4210,7 @@
         <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
@@ -4279,7 +4279,7 @@
         <v>4.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
         <v>10.5</v>
@@ -4309,7 +4309,7 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
         <v>4.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4832,65 +4832,65 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
         <v>2.02</v>
@@ -4936,7 +4936,7 @@
         <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.28</v>
@@ -4945,25 +4945,25 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
         <v>2.32</v>
@@ -4975,34 +4975,34 @@
         <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
@@ -5011,73 +5011,73 @@
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.42</v>
+        <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY18" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.18</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.22</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.18</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
         <v>32</v>
@@ -5092,7 +5092,7 @@
         <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,13 +5104,13 @@
         <v>5.1</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BP18" t="n">
         <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BR18" t="n">
         <v>25</v>
@@ -5122,7 +5122,7 @@
         <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV18" t="n">
         <v>32</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5241,13 +5241,13 @@
         <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>90</v>
@@ -5259,7 +5259,7 @@
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>80</v>
@@ -5268,7 +5268,7 @@
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL19" t="n">
         <v>34</v>
@@ -5295,25 +5295,25 @@
         <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AY19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>1.01</v>
@@ -5346,13 +5346,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN19" t="n">
         <v>4.5</v>
@@ -5364,41 +5364,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5468,7 +5468,7 @@
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5848,65 +5848,65 @@
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6102,65 +6102,65 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -6191,230 +6191,230 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="G23" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="n">
         <v>3.8</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="BI23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV23" t="n">
         <v>23</v>
       </c>
-      <c r="AA23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="BW23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX23" t="n">
         <v>34</v>
       </c>
-      <c r="AO23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BT23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY23" t="n">
-        <v>1.34</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 13:25:02</t>
+          <t>2026-06-18 15:36:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
         <v>1.51</v>
@@ -890,10 +890,10 @@
         <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
         <v>5.1</v>
@@ -902,7 +902,7 @@
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
         <v>1.65</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
@@ -950,7 +950,7 @@
         <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL2" t="n">
         <v>100</v>
@@ -965,58 +965,58 @@
         <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>6.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>6.4</v>
       </c>
       <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
         <v>8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>8</v>
       </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>2.8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J3" t="n">
         <v>2.92</v>
@@ -1147,7 +1147,7 @@
         <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
         <v>3.55</v>
@@ -1156,13 +1156,13 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>12</v>
@@ -1234,7 +1234,7 @@
         <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV3" t="n">
         <v>4.2</v>
@@ -1246,7 +1246,7 @@
         <v>3.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
         <v>4.3</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1401,16 +1401,16 @@
         <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
         <v>1.06</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1419,7 +1419,7 @@
         <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
         <v>1000</v>
@@ -1473,64 +1473,64 @@
         <v>90</v>
       </c>
       <c r="AP4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BA4" t="n">
         <v>1.54</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BB4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1.51</v>
       </c>
-      <c r="AX4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BD4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.52</v>
       </c>
-      <c r="BB4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1619,100 +1619,100 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1721,64 +1721,64 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BH5" t="n">
         <v>3.4</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -1891,7 +1891,7 @@
         <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
@@ -1915,7 +1915,7 @@
         <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1924,10 +1924,10 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="X6" t="n">
-        <v>42</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1939,13 +1939,13 @@
         <v>120</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1954,43 +1954,43 @@
         <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
         <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
@@ -1999,10 +1999,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2014,7 +2014,7 @@
         <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
         <v>13.5</v>
@@ -2026,25 +2026,25 @@
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
         <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BJ6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2062,10 +2062,10 @@
         <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
         <v>8</v>
@@ -2074,7 +2074,7 @@
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G7" t="n">
         <v>4.5</v>
@@ -2136,16 +2136,16 @@
         <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2154,16 +2154,16 @@
         <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
         <v>3.85</v>
@@ -2172,175 +2172,175 @@
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
         <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.09</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.09</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.1</v>
+        <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.09</v>
+        <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.09</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.53</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.69</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.37</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.58</v>
+        <v>6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.63</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2381,37 +2381,37 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
         <v>1.75</v>
@@ -2423,13 +2423,13 @@
         <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="W8" t="n">
         <v>1.19</v>
@@ -2438,25 +2438,25 @@
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>18.5</v>
       </c>
       <c r="AF8" t="n">
         <v>55</v>
@@ -2465,7 +2465,7 @@
         <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>38</v>
@@ -2492,91 +2492,91 @@
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.64</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS8" t="n">
         <v>2.7</v>
       </c>
-      <c r="AS8" t="n">
-        <v>3</v>
-      </c>
       <c r="AT8" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.54</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BP8" t="n">
         <v>48</v>
       </c>
       <c r="BQ8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>2.16</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>2.2</v>
       </c>
       <c r="BT8" t="n">
         <v>5.8</v>
@@ -2588,23 +2588,23 @@
         <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BZ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA8" t="n">
         <v>2.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
         <v>3.35</v>
@@ -2644,19 +2644,19 @@
         <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
         <v>3.25</v>
@@ -2665,22 +2665,22 @@
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.64</v>
@@ -2689,13 +2689,13 @@
         <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2728,10 +2728,10 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2743,55 +2743,55 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
@@ -2800,13 +2800,13 @@
         <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -2889,82 +2889,82 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
         <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
         <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>970</v>
@@ -2976,133 +2976,133 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.24</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.24</v>
+        <v>3.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.24</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.24</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.24</v>
+        <v>3.85</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>3.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.14</v>
+        <v>3.85</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="BJ10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.81</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.72</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.75</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>1.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
         <v>13.5</v>
@@ -3167,7 +3167,7 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
@@ -3176,7 +3176,7 @@
         <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.46</v>
@@ -3185,19 +3185,19 @@
         <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
         <v>950</v>
@@ -3209,10 +3209,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD11" t="n">
         <v>950</v>
@@ -3221,16 +3221,16 @@
         <v>330</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AI11" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
@@ -3242,37 +3242,37 @@
         <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO11" t="n">
         <v>470</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3281,40 +3281,40 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF11" t="n">
         <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="n">
         <v>4.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
         <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -3421,7 +3421,7 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
@@ -3442,79 +3442,79 @@
         <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
         <v>200</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
         <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
         <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO12" t="n">
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.72</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.98</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.05</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3523,94 +3523,94 @@
         <v>8.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.9</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.21</v>
+        <v>5.3</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.21</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.21</v>
+        <v>3.7</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.21</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.17</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.19</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3651,220 +3651,220 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
         <v>1.83</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
         <v>5.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
         <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP13" t="n">
         <v>11</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>12</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.85</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -3905,73 +3905,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>500</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>1.81</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
         <v>970</v>
@@ -3980,10 +3980,10 @@
         <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
         <v>970</v>
@@ -3992,7 +3992,7 @@
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
         <v>970</v>
@@ -4004,67 +4004,67 @@
         <v>40</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE14" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.62</v>
       </c>
       <c r="BF14" t="n">
         <v>6.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -4165,25 +4165,25 @@
         <v>1.35</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
         <v>5.7</v>
       </c>
       <c r="K15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
@@ -4192,7 +4192,7 @@
         <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
         <v>1.59</v>
@@ -4207,7 +4207,7 @@
         <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
         <v>3.85</v>
@@ -4228,16 +4228,16 @@
         <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD15" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
@@ -4249,7 +4249,7 @@
         <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK15" t="n">
         <v>17.5</v>
@@ -4261,7 +4261,7 @@
         <v>180</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AO15" t="n">
         <v>280</v>
@@ -4270,13 +4270,13 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -4285,10 +4285,10 @@
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,16 +4309,16 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
         <v>3.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>4.7</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -4413,230 +4413,230 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,22 +4691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="O17" t="n">
         <v>1.05</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q17" t="n">
         <v>1.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>3.9</v>
@@ -4933,13 +4933,13 @@
         <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -4948,31 +4948,31 @@
         <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
         <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>23</v>
@@ -4990,13 +4990,13 @@
         <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
         <v>15.5</v>
@@ -5005,25 +5005,25 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO18" t="n">
         <v>55</v>
@@ -5035,52 +5035,52 @@
         <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX18" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AY18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BH18" t="n">
         <v>4.1</v>
@@ -5092,7 +5092,7 @@
         <v>9.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5110,7 +5110,7 @@
         <v>14</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR18" t="n">
         <v>25</v>
@@ -5122,7 +5122,7 @@
         <v>7.8</v>
       </c>
       <c r="BU18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV18" t="n">
         <v>32</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
         <v>1.58</v>
@@ -5205,22 +5205,22 @@
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
         <v>1.16</v>
@@ -5232,7 +5232,7 @@
         <v>34</v>
       </c>
       <c r="Y19" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z19" t="n">
         <v>70</v>
@@ -5241,25 +5241,25 @@
         <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AE19" t="n">
         <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
         <v>80</v>
@@ -5268,16 +5268,16 @@
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
         <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO19" t="n">
         <v>80</v>
@@ -5286,37 +5286,37 @@
         <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -5325,16 +5325,16 @@
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="n">
         <v>4.7</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
         <v>4.5</v>
@@ -5367,7 +5367,7 @@
         <v>5.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS19" t="n">
         <v>8.199999999999999</v>
@@ -5391,14 +5391,14 @@
         <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA19" t="n">
         <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5429,178 +5429,178 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M20" t="n">
         <v>1.02</v>
       </c>
-      <c r="G20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N20" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,31 +5612,31 @@
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
@@ -5648,11 +5648,11 @@
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5683,230 +5683,230 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -5937,160 +5937,160 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.02</v>
+        <v>1.85</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P22" t="n">
         <v>1.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>3.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP22" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6099,68 +6099,68 @@
         <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6191,230 +6191,230 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="H23" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP23" t="n">
         <v>3.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="AQ23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE23" t="n">
         <v>4.1</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 15:36:00</t>
+          <t>2026-06-18 17:47:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,43 +857,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
         <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
         <v>5.1</v>
@@ -902,16 +902,16 @@
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.65</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>7.6</v>
@@ -920,7 +920,7 @@
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
@@ -944,19 +944,19 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AJ2" t="n">
         <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AM2" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
         <v>110</v>
@@ -965,58 +965,58 @@
         <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>7</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7</v>
       </c>
       <c r="BH2" t="n">
         <v>2.8</v>
@@ -1040,7 +1040,7 @@
         <v>7.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
         <v>40</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA2" t="n">
         <v>2.16</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1120,10 +1120,10 @@
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1135,7 +1135,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
@@ -1150,7 +1150,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
@@ -1159,118 +1159,118 @@
         <v>1.77</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
         <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF3" t="n">
         <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AR3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX3" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>3.25</v>
@@ -1401,16 +1401,16 @@
         <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
         <v>1.06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
@@ -1422,31 +1422,31 @@
         <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
         <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>28</v>
@@ -1455,16 +1455,16 @@
         <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
         <v>55</v>
@@ -1473,58 +1473,58 @@
         <v>90</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.56</v>
+        <v>2.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.47</v>
+        <v>3.65</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.56</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.34</v>
+        <v>2.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.44</v>
+        <v>3.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.56</v>
+        <v>3.35</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.56</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.54</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.52</v>
+        <v>3.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1640,37 +1640,37 @@
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
         <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
         <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1679,106 +1679,106 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>950</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.64</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.42</v>
+        <v>5.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.48</v>
+        <v>5.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.22</v>
+        <v>5.1</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.48</v>
+        <v>5.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.48</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.72</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.72</v>
+        <v>4.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.36</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -1888,7 +1888,7 @@
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.19</v>
@@ -1897,7 +1897,7 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1.14</v>
@@ -1924,10 +1924,10 @@
         <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1936,7 +1936,7 @@
         <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>16</v>
@@ -1945,7 +1945,7 @@
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1957,13 +1957,13 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
         <v>16</v>
@@ -1972,16 +1972,16 @@
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="n">
         <v>5.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>32</v>
+        <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
@@ -1999,7 +1999,7 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
@@ -2154,10 +2154,10 @@
         <v>3.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
@@ -2169,16 +2169,16 @@
         <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -2202,7 +2202,7 @@
         <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>34</v>
@@ -2214,22 +2214,22 @@
         <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
         <v>60</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO7" t="n">
         <v>16.5</v>
@@ -2259,7 +2259,7 @@
         <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AY7" t="n">
         <v>14.5</v>
@@ -2268,22 +2268,22 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
         <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
         <v>13.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2387,10 +2387,10 @@
         <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="I8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2399,13 +2399,13 @@
         <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
@@ -2423,67 +2423,67 @@
         <v>2.82</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z8" t="n">
         <v>11</v>
       </c>
-      <c r="Z8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AA8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH8" t="n">
         <v>21</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
       <c r="AI8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
         <v>90</v>
       </c>
       <c r="AL8" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AO8" t="n">
         <v>8.6</v>
@@ -2498,22 +2498,22 @@
         <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.1</v>
+        <v>16.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.44</v>
+        <v>5.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.68</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.94</v>
+        <v>6.8</v>
       </c>
       <c r="AY8" t="n">
         <v>16.5</v>
@@ -2522,22 +2522,22 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.86</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.1</v>
+        <v>7.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
         <v>6.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9" t="n">
         <v>3.3</v>
@@ -2653,22 +2653,22 @@
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
@@ -2677,10 +2677,10 @@
         <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
         <v>1.64</v>
@@ -2689,109 +2689,109 @@
         <v>1.42</v>
       </c>
       <c r="X9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>970</v>
       </c>
-      <c r="Y9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.23</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.24</v>
+        <v>3.45</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.14</v>
+        <v>6.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.24</v>
+        <v>3.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.21</v>
+        <v>3.55</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
@@ -2800,10 +2800,10 @@
         <v>3.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
         <v>5.2</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>6.6</v>
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT9" t="n">
         <v>5.5</v>
@@ -2842,13 +2842,13 @@
         <v>19.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
         <v>36</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
         <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
         <v>3.45</v>
@@ -2913,46 +2913,46 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W10" t="n">
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
         <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>13.5</v>
@@ -2961,64 +2961,64 @@
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
@@ -3027,28 +3027,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.75</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
         <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K11" t="n">
         <v>6.6</v>
@@ -3167,7 +3167,7 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
@@ -3179,28 +3179,28 @@
         <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
         <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>140</v>
       </c>
       <c r="Z11" t="n">
         <v>160</v>
@@ -3212,13 +3212,13 @@
         <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>300</v>
       </c>
       <c r="AE11" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AF11" t="n">
         <v>7.6</v>
@@ -3227,22 +3227,22 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
         <v>5.7</v>
@@ -3254,13 +3254,13 @@
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3269,10 +3269,10 @@
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3284,7 +3284,7 @@
         <v>32</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>8.4</v>
@@ -3296,13 +3296,13 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
         <v>4.3</v>
@@ -3332,7 +3332,7 @@
         <v>7.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
         <v>36</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="H12" t="n">
         <v>5.7</v>
@@ -3409,13 +3409,13 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3427,28 +3427,28 @@
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -3457,10 +3457,10 @@
         <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
         <v>9.6</v>
@@ -3472,7 +3472,7 @@
         <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AF12" t="n">
         <v>11</v>
@@ -3484,25 +3484,25 @@
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AJ12" t="n">
         <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
         <v>13</v>
@@ -3511,10 +3511,10 @@
         <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
@@ -3526,7 +3526,7 @@
         <v>17</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX12" t="n">
         <v>7.6</v>
@@ -3538,7 +3538,7 @@
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB12" t="n">
         <v>13.5</v>
@@ -3547,28 +3547,28 @@
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
         <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,13 +3580,13 @@
         <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP12" t="n">
         <v>11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
         <v>26</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3663,43 +3663,43 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
         <v>2.2</v>
@@ -3711,10 +3711,10 @@
         <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>9.4</v>
@@ -3726,7 +3726,7 @@
         <v>29</v>
       </c>
       <c r="AE13" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
         <v>12</v>
@@ -3738,7 +3738,7 @@
         <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
@@ -3747,16 +3747,16 @@
         <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -3765,10 +3765,10 @@
         <v>13.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3777,10 +3777,10 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
         <v>8.199999999999999</v>
@@ -3789,28 +3789,28 @@
         <v>7.8</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BD13" t="n">
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF13" t="n">
         <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>3.45</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN13" t="n">
         <v>4.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="G14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3929,142 +3929,142 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>2.16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="n">
         <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AO14" t="n">
-        <v>95</v>
+        <v>700</v>
       </c>
       <c r="AP14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY14" t="n">
         <v>4.9</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4171,10 +4171,10 @@
         <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.27</v>
@@ -4183,28 +4183,28 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -4213,22 +4213,22 @@
         <v>3.85</v>
       </c>
       <c r="X15" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Z15" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AA15" t="n">
         <v>530</v>
       </c>
       <c r="AB15" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -4237,16 +4237,16 @@
         <v>220</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
-        <v>170</v>
+        <v>460</v>
       </c>
       <c r="AJ15" t="n">
         <v>11</v>
@@ -4255,7 +4255,7 @@
         <v>17.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
         <v>180</v>
@@ -4270,13 +4270,13 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -4285,10 +4285,10 @@
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
         <v>6.6</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,22 +4309,22 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ15" t="n">
         <v>12.5</v>
@@ -4342,7 +4342,7 @@
         <v>4</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
         <v>7.6</v>
@@ -4375,14 +4375,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         <v>1.08</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
         <v>1.24</v>
@@ -4461,16 +4461,16 @@
         <v>2.88</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W16" t="n">
         <v>2.66</v>
       </c>
       <c r="X16" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="Y16" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="Z16" t="n">
         <v>85</v>
@@ -4479,7 +4479,7 @@
         <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -4488,7 +4488,7 @@
         <v>36</v>
       </c>
       <c r="AE16" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF16" t="n">
         <v>970</v>
@@ -4500,16 +4500,16 @@
         <v>970</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
         <v>970</v>
       </c>
       <c r="AL16" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>55</v>
@@ -4521,7 +4521,7 @@
         <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.4</v>
@@ -4530,13 +4530,13 @@
         <v>6.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV16" t="n">
         <v>5.7</v>
@@ -4548,16 +4548,16 @@
         <v>5.2</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
         <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
         <v>4.9</v>
@@ -4566,13 +4566,13 @@
         <v>5.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
         <v>2.62</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4718,61 +4718,61 @@
         <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>1.03</v>
@@ -4823,7 +4823,7 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
         <v>1.01</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
         <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.33</v>
@@ -4951,22 +4951,22 @@
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
@@ -4981,7 +4981,7 @@
         <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
         <v>95</v>
@@ -4990,37 +4990,37 @@
         <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
         <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
         <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>14.5</v>
@@ -5035,22 +5035,22 @@
         <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -5071,16 +5071,16 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>14.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="n">
         <v>4.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G19" t="n">
         <v>1.58</v>
@@ -5184,7 +5184,7 @@
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>4.8</v>
@@ -5223,46 +5223,46 @@
         <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
         <v>2.72</v>
       </c>
       <c r="X19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y19" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA19" t="n">
         <v>190</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE19" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="AF19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -5271,70 +5271,70 @@
         <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AO19" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AP19" t="n">
         <v>20</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
         <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC19" t="n">
         <v>10.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="n">
         <v>4.7</v>
@@ -5346,7 +5346,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="G20" t="n">
         <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I20" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>1.17</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
         <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="U20" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5489,118 +5489,118 @@
         <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
         <v>950</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AG20" t="n">
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>48</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>48</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AO20" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="AS20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
         <v>3.85</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,31 +5612,31 @@
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
@@ -5648,11 +5648,11 @@
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G21" t="n">
         <v>2.2</v>
@@ -5695,7 +5695,7 @@
         <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
         <v>5.2</v>
@@ -5707,7 +5707,7 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
         <v>1.1</v>
@@ -5722,10 +5722,10 @@
         <v>2.06</v>
       </c>
       <c r="S21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T21" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="U21" t="n">
         <v>3.25</v>
@@ -5734,115 +5734,115 @@
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA21" t="n">
         <v>60</v>
       </c>
-      <c r="Y21" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>65</v>
-      </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AC21" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
         <v>19.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
         <v>27</v>
       </c>
       <c r="AG21" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
         <v>16.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL21" t="n">
         <v>22</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>25</v>
       </c>
       <c r="AM21" t="n">
         <v>42</v>
       </c>
       <c r="AN21" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.85</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="n">
         <v>6.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -5943,13 +5943,13 @@
         <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
         <v>5.7</v>
@@ -5961,28 +5961,28 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="O22" t="n">
         <v>1.06</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="S22" t="n">
         <v>1.51</v>
       </c>
       <c r="T22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="U22" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
@@ -5991,7 +5991,7 @@
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Y22" t="n">
         <v>55</v>
@@ -6006,97 +6006,97 @@
         <v>42</v>
       </c>
       <c r="AC22" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>36</v>
       </c>
       <c r="AG22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AJ22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL22" t="n">
         <v>38</v>
       </c>
-      <c r="AK22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>23</v>
-      </c>
       <c r="AM22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AO22" t="n">
         <v>12.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH22" t="n">
         <v>7.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6191,103 +6191,103 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G23" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H23" t="n">
         <v>2.72</v>
       </c>
       <c r="I23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.15</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.74</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM23" t="n">
         <v>120</v>
@@ -6299,58 +6299,58 @@
         <v>38</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.24</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H24" t="n">
-        <v>1.26</v>
+        <v>2.44</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 17:47:02</t>
+          <t>2026-06-18 19:58:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -863,13 +863,13 @@
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
         <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
         <v>3.25</v>
@@ -881,7 +881,7 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O2" t="n">
         <v>1.52</v>
@@ -896,7 +896,7 @@
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>2.06</v>
@@ -905,7 +905,7 @@
         <v>1.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W2" t="n">
         <v>1.32</v>
@@ -965,7 +965,7 @@
         <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.5</v>
@@ -995,7 +995,7 @@
         <v>6.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA2" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
         <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
@@ -1135,10 +1135,10 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
@@ -1189,13 +1189,13 @@
         <v>210</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>240</v>
@@ -1210,73 +1210,73 @@
         <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6</v>
       </c>
-      <c r="AS3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="BD3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
         <v>12</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
@@ -1419,7 +1419,7 @@
         <v>1.57</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
         <v>9.800000000000001</v>
@@ -1434,7 +1434,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
@@ -1473,58 +1473,58 @@
         <v>90</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AU4" t="n">
-        <v>2.72</v>
+        <v>3.85</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.35</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
         <v>2.78</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
         <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
@@ -1652,31 +1652,31 @@
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
         <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,34 +1685,34 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
         <v>500</v>
@@ -1721,7 +1721,7 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
@@ -1730,55 +1730,55 @@
         <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD5" t="n">
         <v>7</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
         <v>3.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -2145,7 +2145,7 @@
         <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -2184,7 +2184,7 @@
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
@@ -2205,7 +2205,7 @@
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AG7" t="n">
         <v>18</v>
@@ -2220,16 +2220,16 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AO7" t="n">
         <v>16.5</v>
@@ -2250,7 +2250,7 @@
         <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -2268,79 +2268,79 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="BJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BN7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>1.76</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>1.66</v>
       </c>
       <c r="BX7" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>1.74</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G8" t="n">
         <v>6.2</v>
@@ -2390,7 +2390,7 @@
         <v>1.66</v>
       </c>
       <c r="I8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
         <v>4.3</v>
@@ -2426,10 +2426,10 @@
         <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W8" t="n">
         <v>1.2</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG8" t="n">
         <v>26</v>
@@ -2525,10 +2525,10 @@
         <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD8" t="n">
         <v>7.2</v>
@@ -2546,34 +2546,34 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BN8" t="n">
         <v>13</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BP8" t="n">
         <v>48</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8" t="n">
         <v>2.16</v>
@@ -2588,23 +2588,23 @@
         <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
@@ -2668,7 +2668,7 @@
         <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
@@ -2752,7 +2752,7 @@
         <v>3.45</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
         <v>10</v>
@@ -2782,13 +2782,13 @@
         <v>3.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.55</v>
+        <v>32</v>
       </c>
       <c r="BD9" t="n">
         <v>3.85</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BF9" t="n">
         <v>3.55</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -2889,64 +2889,64 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.72</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.84</v>
-      </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,22 +2955,22 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
         <v>36</v>
@@ -3006,7 +3006,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>5.8</v>
@@ -3018,7 +3018,7 @@
         <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>12.5</v>
@@ -3027,70 +3027,70 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
         <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>4.7</v>
@@ -3173,22 +3173,22 @@
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
         <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.06</v>
@@ -3218,7 +3218,7 @@
         <v>300</v>
       </c>
       <c r="AE11" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AF11" t="n">
         <v>7.6</v>
@@ -3230,22 +3230,22 @@
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL11" t="n">
         <v>160</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO11" t="n">
         <v>470</v>
@@ -3254,13 +3254,13 @@
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -3269,10 +3269,10 @@
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3281,10 +3281,10 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11" t="n">
         <v>8.4</v>
@@ -3293,10 +3293,10 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>4.7</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.59</v>
       </c>
       <c r="G12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
         <v>5.7</v>
@@ -3409,208 +3409,208 @@
         <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>25</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AK12" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>13</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="BB12" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BC12" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
         <v>5.1</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -3905,25 +3905,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3938,28 +3938,28 @@
         <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
@@ -3971,22 +3971,22 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -3995,10 +3995,10 @@
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4013,112 +4013,112 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>2.46</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.6</v>
+        <v>2.34</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB14" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB14" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC14" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>2.56</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="K15" t="n">
         <v>6.8</v>
@@ -4216,7 +4216,7 @@
         <v>70</v>
       </c>
       <c r="Y15" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="Z15" t="n">
         <v>540</v>
@@ -4240,7 +4240,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>32</v>
@@ -4252,10 +4252,10 @@
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
         <v>180</v>
@@ -4273,10 +4273,10 @@
         <v>14.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -4285,13 +4285,13 @@
         <v>10.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY15" t="n">
         <v>8.199999999999999</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
         <v>7.8</v>
@@ -4309,10 +4309,10 @@
         <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
         <v>4.1</v>
@@ -4342,7 +4342,7 @@
         <v>4</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BP15" t="n">
         <v>7.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
@@ -4467,10 +4467,10 @@
         <v>2.66</v>
       </c>
       <c r="X16" t="n">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>130</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
         <v>85</v>
@@ -4485,7 +4485,7 @@
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
         <v>160</v>
@@ -4521,7 +4521,7 @@
         <v>34</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.94</v>
+        <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
         <v>6.4</v>
@@ -4569,7 +4569,7 @@
         <v>6.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BG16" t="n">
         <v>5.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>14.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4718,13 +4718,13 @@
         <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
         <v>500</v>
@@ -4733,13 +4733,13 @@
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
         <v>500</v>
       </c>
       <c r="AD17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
@@ -4748,10 +4748,10 @@
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
@@ -4775,58 +4775,58 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU17" t="n">
         <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>4.4</v>
@@ -4963,7 +4963,7 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
         <v>2.24</v>
@@ -4984,7 +4984,7 @@
         <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
         <v>13</v>
@@ -5014,7 +5014,7 @@
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>36</v>
@@ -5038,7 +5038,7 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -5074,7 +5074,7 @@
         <v>14.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>5.1</v>
@@ -5107,7 +5107,7 @@
         <v>4.2</v>
       </c>
       <c r="BP18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>8</v>
@@ -5116,7 +5116,7 @@
         <v>25</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
         <v>7.8</v>
@@ -5128,13 +5128,13 @@
         <v>32</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX18" t="n">
         <v>38</v>
       </c>
       <c r="BY18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J19" t="n">
         <v>4.8</v>
@@ -5205,7 +5205,7 @@
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
         <v>1.51</v>
@@ -5328,13 +5328,13 @@
         <v>19.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
         <v>5</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH19" t="n">
         <v>4.7</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
         <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>2.88</v>
@@ -5465,7 +5465,7 @@
         <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S20" t="n">
         <v>1.76</v>
@@ -5474,7 +5474,7 @@
         <v>1.37</v>
       </c>
       <c r="U20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V20" t="n">
         <v>1.55</v>
@@ -5537,7 +5537,7 @@
         <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AQ20" t="n">
         <v>5.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>1.97</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
         <v>3.05</v>
@@ -5782,7 +5782,7 @@
         <v>22</v>
       </c>
       <c r="AM21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AN21" t="n">
         <v>6.6</v>
@@ -5794,13 +5794,13 @@
         <v>7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR21" t="n">
         <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>18</v>
@@ -5812,10 +5812,10 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX21" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -5827,7 +5827,7 @@
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>14</v>
@@ -5842,7 +5842,7 @@
         <v>5.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH21" t="n">
         <v>6.4</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
         <v>55</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
         <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
@@ -6236,7 +6236,7 @@
         <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.48</v>
@@ -6248,7 +6248,7 @@
         <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z23" t="n">
         <v>24</v>
@@ -6299,28 +6299,28 @@
         <v>38</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ23" t="n">
         <v>3.95</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX23" t="n">
         <v>12.5</v>
@@ -6329,28 +6329,28 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC23" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BD23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF23" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
         <v>3.95</v>
       </c>
       <c r="H24" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
         <v>2.72</v>
@@ -6463,7 +6463,7 @@
         <v>3.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="M24" t="n">
         <v>1.14</v>
@@ -6487,7 +6487,7 @@
         <v>6.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
         <v>1.68</v>
@@ -6553,28 +6553,28 @@
         <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR24" t="n">
         <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 19:58:30</t>
+          <t>2026-06-18 22:10:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
@@ -869,10 +869,10 @@
         <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
@@ -881,7 +881,7 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
         <v>1.52</v>
@@ -890,16 +890,16 @@
         <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
         <v>1.76</v>
@@ -908,10 +908,10 @@
         <v>1.66</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y2" t="n">
         <v>7.6</v>
@@ -938,7 +938,7 @@
         <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -947,7 +947,7 @@
         <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
         <v>70</v>
@@ -968,13 +968,13 @@
         <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
         <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>5.6</v>
@@ -986,40 +986,40 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF2" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI2" t="n">
         <v>2.46</v>
@@ -1028,59 +1028,59 @@
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
         <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
         <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2" t="n">
         <v>50</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1135,10 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
         <v>1.59</v>
@@ -1150,7 +1150,7 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AF4" t="n">
         <v>16</v>
@@ -1476,13 +1476,13 @@
         <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>4</v>
@@ -1491,16 +1491,16 @@
         <v>3.85</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
         <v>6.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AZ4" t="n">
         <v>6</v>
@@ -1509,19 +1509,19 @@
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC4" t="n">
         <v>6.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE4" t="n">
         <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
         <v>7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1643,28 +1643,28 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R5" t="n">
         <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>1.19</v>
@@ -1673,10 +1673,10 @@
         <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,13 +1685,13 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1700,16 +1700,16 @@
         <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>70</v>
@@ -1727,16 +1727,16 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1760,7 +1760,7 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
         <v>8.4</v>
@@ -1769,16 +1769,16 @@
         <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.4</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.66</v>
+        <v>6.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
         <v>1.75</v>
@@ -1891,31 +1891,31 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1939,7 +1939,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
@@ -1987,10 +1987,10 @@
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>11.5</v>
@@ -2002,7 +2002,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2026,16 +2026,16 @@
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI6" t="n">
         <v>4.6</v>
@@ -2044,16 +2044,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO6" t="n">
         <v>4.5</v>
@@ -2062,13 +2062,13 @@
         <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -2139,10 +2139,10 @@
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
@@ -2157,7 +2157,7 @@
         <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
@@ -2166,7 +2166,7 @@
         <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.8</v>
@@ -2178,13 +2178,13 @@
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
@@ -2199,7 +2199,7 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -2253,7 +2253,7 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AW7" t="n">
         <v>18.5</v>
@@ -2268,19 +2268,19 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD7" t="n">
         <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF7" t="n">
         <v>9.800000000000001</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2387,16 +2387,16 @@
         <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I8" t="n">
         <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2414,7 +2414,7 @@
         <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -2447,13 +2447,13 @@
         <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD8" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>17.5</v>
@@ -2462,7 +2462,7 @@
         <v>48</v>
       </c>
       <c r="AG8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -2498,10 +2498,10 @@
         <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>5.6</v>
@@ -2510,73 +2510,73 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD8" t="n">
         <v>8</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BE8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG8" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH8" t="n">
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BN8" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BO8" t="n">
         <v>1.93</v>
       </c>
       <c r="BP8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BR8" t="n">
         <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BT8" t="n">
         <v>5.8</v>
@@ -2588,23 +2588,23 @@
         <v>11</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2644,10 +2644,10 @@
         <v>2.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2659,28 +2659,28 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.64</v>
@@ -2689,10 +2689,10 @@
         <v>1.42</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
         <v>970</v>
@@ -2710,7 +2710,7 @@
         <v>13.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
@@ -2722,7 +2722,7 @@
         <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AJ9" t="n">
         <v>65</v>
@@ -2749,7 +2749,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
         <v>14.5</v>
@@ -2761,43 +2761,43 @@
         <v>4.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI9" t="n">
         <v>2.7</v>
@@ -2806,13 +2806,13 @@
         <v>10</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6.6</v>
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT9" t="n">
         <v>5.5</v>
@@ -2842,13 +2842,13 @@
         <v>19.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX9" t="n">
         <v>36</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -2895,10 +2895,10 @@
         <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.3</v>
@@ -2907,7 +2907,7 @@
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2937,7 +2937,7 @@
         <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
         <v>1.54</v>
@@ -3090,7 +3090,7 @@
         <v>6.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.28</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>16</v>
@@ -3167,7 +3167,7 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.24</v>
@@ -3176,16 +3176,16 @@
         <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
         <v>1.72</v>
@@ -3194,13 +3194,13 @@
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="Z11" t="n">
         <v>160</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
         <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
         <v>2.84</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H13" t="n">
         <v>5.1</v>
@@ -3663,7 +3663,7 @@
         <v>5.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>4.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.75</v>
@@ -3956,7 +3956,7 @@
         <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3977,7 +3977,7 @@
         <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
@@ -4013,19 +4013,19 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
@@ -4034,7 +4034,7 @@
         <v>2.34</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4052,19 +4052,19 @@
         <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BF14" t="n">
         <v>7.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>1.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I15" t="n">
         <v>13.5</v>
@@ -4192,13 +4192,13 @@
         <v>2.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
         <v>2.02</v>
@@ -4210,7 +4210,7 @@
         <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="X15" t="n">
         <v>70</v>
@@ -4342,7 +4342,7 @@
         <v>4</v>
       </c>
       <c r="BO15" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
         <v>7.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I18" t="n">
         <v>4.4</v>
@@ -4963,7 +4963,7 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
         <v>2.24</v>
@@ -5023,7 +5023,7 @@
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>55</v>
@@ -5038,7 +5038,7 @@
         <v>14.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -5074,7 +5074,7 @@
         <v>14.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.49</v>
       </c>
       <c r="G19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
@@ -5190,7 +5190,7 @@
         <v>4.8</v>
       </c>
       <c r="K19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.22</v>
@@ -5199,19 +5199,19 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
         <v>2.26</v>
@@ -5220,13 +5220,13 @@
         <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X19" t="n">
         <v>36</v>
@@ -5328,31 +5328,31 @@
         <v>19.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG19" t="n">
         <v>4.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.5</v>
@@ -5361,16 +5361,16 @@
         <v>3.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA19" t="n">
         <v>6.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="I20" t="n">
         <v>2.88</v>
@@ -5465,7 +5465,7 @@
         <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S20" t="n">
         <v>1.76</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -5970,19 +5970,19 @@
         <v>4.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
         <v>1.28</v>
       </c>
       <c r="U22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="V22" t="n">
         <v>1.37</v>
@@ -5994,7 +5994,7 @@
         <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>60</v>
@@ -6003,7 +6003,7 @@
         <v>85</v>
       </c>
       <c r="AB22" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AC22" t="n">
         <v>18.5</v>
@@ -6045,19 +6045,19 @@
         <v>12.5</v>
       </c>
       <c r="AP22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT22" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -6066,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -6081,7 +6081,7 @@
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -6090,13 +6090,13 @@
         <v>13.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF22" t="n">
         <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="n">
         <v>7.8</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2.86</v>
       </c>
       <c r="H23" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I23" t="n">
         <v>3.05</v>
@@ -6215,28 +6215,28 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
         <v>1.48</v>
@@ -6248,10 +6248,10 @@
         <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
         <v>50</v>
@@ -6275,7 +6275,7 @@
         <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>55</v>
@@ -6290,7 +6290,7 @@
         <v>50</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>32</v>
@@ -6299,58 +6299,58 @@
         <v>38</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AR23" t="n">
         <v>4.9</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU23" t="n">
         <v>6.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX23" t="n">
         <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB23" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BC23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG23" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>5.3</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>
@@ -6445,67 +6445,67 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I24" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J24" t="n">
         <v>2.78</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.63</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.61</v>
-      </c>
       <c r="P24" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R24" t="n">
         <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W24" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
         <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
         <v>900</v>
@@ -6556,16 +6556,16 @@
         <v>6.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR24" t="n">
         <v>10.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU24" t="n">
         <v>6</v>
@@ -6574,7 +6574,7 @@
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
         <v>17</v>
@@ -6586,28 +6586,28 @@
         <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.9</v>
       </c>
-      <c r="BE24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH24" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BI24" t="n">
         <v>2.3</v>
@@ -6625,16 +6625,16 @@
         <v>12</v>
       </c>
       <c r="BN24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
@@ -6643,13 +6643,13 @@
         <v>10.5</v>
       </c>
       <c r="BT24" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BV24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BW24" t="n">
         <v>8.4</v>
@@ -6664,11 +6664,11 @@
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-18 22:10:16</t>
+          <t>2026-06-19 00:23:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
@@ -866,55 +866,55 @@
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>14</v>
@@ -923,7 +923,7 @@
         <v>36</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
@@ -932,40 +932,40 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
         <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.6</v>
@@ -974,7 +974,7 @@
         <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>5.6</v>
@@ -986,101 +986,101 @@
         <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB2" t="n">
         <v>9</v>
       </c>
-      <c r="BB2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.26</v>
+        <v>150</v>
       </c>
       <c r="BN2" t="n">
         <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1183,7 +1183,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>210</v>
@@ -1213,34 +1213,34 @@
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
         <v>5</v>
@@ -1249,28 +1249,28 @@
         <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD3" t="n">
         <v>7</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
         <v>5.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.28</v>
+        <v>140</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1365,67 +1365,67 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
@@ -1443,152 +1443,152 @@
         <v>150</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
         <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AJ4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL4" t="n">
         <v>170</v>
       </c>
       <c r="AM4" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="AV4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6</v>
       </c>
-      <c r="AS4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AY4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="BN4" t="n">
         <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.14</v>
+        <v>8.6</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.14</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,13 +1685,13 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1733,10 +1733,10 @@
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1748,7 +1748,7 @@
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1760,61 +1760,61 @@
         <v>13</v>
       </c>
       <c r="BA5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>8</v>
       </c>
-      <c r="BB5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="BN5" t="n">
         <v>4.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -1876,58 +1876,58 @@
         <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="S6" t="n">
         <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X6" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1939,13 +1939,13 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1966,85 +1966,85 @@
         <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AO6" t="n">
         <v>270</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR6" t="n">
         <v>20</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>11.5</v>
       </c>
       <c r="BD6" t="n">
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BF6" t="n">
         <v>5.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BH6" t="n">
         <v>5.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2068,25 +2068,25 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
@@ -2145,43 +2145,43 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
         <v>9.199999999999999</v>
@@ -2253,37 +2253,37 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW7" t="n">
         <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AY7" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="BG7" t="n">
         <v>13</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2384,52 +2384,52 @@
         <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.2</v>
@@ -2450,7 +2450,7 @@
         <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG8" t="n">
         <v>25</v>
@@ -2474,7 +2474,7 @@
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
         <v>160</v>
@@ -2492,16 +2492,16 @@
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
         <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>5.6</v>
@@ -2510,10 +2510,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY8" t="n">
         <v>18</v>
@@ -2522,22 +2522,22 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8" t="n">
         <v>7.4</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2635,55 +2635,55 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
         <v>3.35</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I9" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
         <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W9" t="n">
         <v>1.42</v>
@@ -2695,22 +2695,22 @@
         <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
@@ -2719,10 +2719,10 @@
         <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AI9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
         <v>65</v>
@@ -2734,13 +2734,13 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP9" t="n">
         <v>6.4</v>
@@ -2749,7 +2749,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AS9" t="n">
         <v>14.5</v>
@@ -2758,40 +2758,40 @@
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.95</v>
+        <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.6</v>
+        <v>42</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG9" t="n">
         <v>18</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN9" t="n">
         <v>6.6</v>
@@ -2824,31 +2824,31 @@
         <v>28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU9" t="n">
         <v>4.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -2892,61 +2892,61 @@
         <v>2.58</v>
       </c>
       <c r="G10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.86</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
         <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2958,7 +2958,7 @@
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2967,13 +2967,13 @@
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2997,13 +2997,13 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS10" t="n">
         <v>7</v>
@@ -3012,43 +3012,43 @@
         <v>5.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>6.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
         <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>3.45</v>
       </c>
       <c r="BF10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.45</v>
@@ -3060,37 +3060,37 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT10" t="n">
         <v>6.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
         <v>16</v>
@@ -3161,10 +3161,10 @@
         <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
         <v>4.8</v>
@@ -3173,28 +3173,28 @@
         <v>1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
         <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
@@ -3215,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="AD11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE11" t="n">
         <v>300</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>310</v>
       </c>
       <c r="AF11" t="n">
         <v>7.6</v>
@@ -3227,10 +3227,10 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ11" t="n">
         <v>10</v>
@@ -3239,7 +3239,7 @@
         <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AM11" t="n">
         <v>270</v>
@@ -3248,16 +3248,16 @@
         <v>5.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AP11" t="n">
         <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
@@ -3269,10 +3269,10 @@
         <v>11.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>6.2</v>
@@ -3281,25 +3281,25 @@
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
@@ -3314,16 +3314,16 @@
         <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BO11" t="n">
         <v>3.15</v>
@@ -3338,35 +3338,35 @@
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BZ11" t="n">
         <v>15.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
         <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X12" t="n">
         <v>20</v>
@@ -3505,64 +3505,64 @@
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>3.05</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>15</v>
+        <v>3.05</v>
       </c>
       <c r="AW12" t="n">
         <v>3.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>3.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.7</v>
+        <v>2.64</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BH12" t="n">
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
@@ -3574,43 +3574,43 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -3675,22 +3675,22 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.84</v>
@@ -3699,16 +3699,16 @@
         <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z13" t="n">
         <v>95</v>
@@ -3717,139 +3717,139 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="n">
         <v>22</v>
       </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
       <c r="AL13" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AX13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BG13" t="n">
         <v>12.5</v>
       </c>
-      <c r="BD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BN13" t="n">
         <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU13" t="n">
         <v>5.5</v>
@@ -3858,13 +3858,13 @@
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>12</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -3905,58 +3905,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
@@ -3974,7 +3974,7 @@
         <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -4013,16 +4013,16 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="AQ14" t="n">
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -4031,10 +4031,10 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="AX14" t="n">
         <v>8.199999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="BB14" t="n">
         <v>8.4</v>
@@ -4058,34 +4058,34 @@
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
         <v>13.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
         <v>3.1</v>
@@ -4100,25 +4100,25 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BT14" t="n">
         <v>12</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>1.89</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.9</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4159,64 +4159,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
         <v>12.5</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" t="n">
         <v>6.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="n">
         <v>70</v>
       </c>
       <c r="Y15" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="Z15" t="n">
         <v>540</v>
@@ -4267,58 +4267,58 @@
         <v>280</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW15" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY15" t="n">
+      <c r="BB15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>8</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
         <v>4.6</v>
@@ -4330,19 +4330,19 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP15" t="n">
         <v>7.6</v>
@@ -4354,35 +4354,35 @@
         <v>23</v>
       </c>
       <c r="BS15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT15" t="n">
         <v>15</v>
       </c>
       <c r="BU15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>11.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H16" t="n">
         <v>4.5</v>
@@ -4431,40 +4431,40 @@
         <v>8.4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.24</v>
       </c>
       <c r="R16" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="S16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4494,7 +4494,7 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
         <v>970</v>
@@ -4503,7 +4503,7 @@
         <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
         <v>970</v>
@@ -4515,7 +4515,7 @@
         <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AO16" t="n">
         <v>34</v>
@@ -4524,25 +4524,25 @@
         <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR16" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.6</v>
       </c>
       <c r="AS16" t="n">
         <v>4.2</v>
       </c>
       <c r="AT16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV16" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>5.2</v>
@@ -4551,34 +4551,34 @@
         <v>4.7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB16" t="n">
         <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4590,10 +4590,10 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO16" t="n">
         <v>3.35</v>
@@ -4602,41 +4602,41 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.53</v>
+        <v>2.56</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4775,58 +4775,58 @@
         <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -4921,55 +4921,55 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
         <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -4981,16 +4981,16 @@
         <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
         <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
         <v>17</v>
@@ -4999,7 +4999,7 @@
         <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -5020,7 +5020,7 @@
         <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
         <v>13</v>
@@ -5035,10 +5035,10 @@
         <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.7</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5050,7 +5050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
         <v>9.4</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BB18" t="n">
         <v>15.5</v>
@@ -5071,22 +5071,22 @@
         <v>15</v>
       </c>
       <c r="BD18" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.8</v>
+        <v>55</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
         <v>5.1</v>
@@ -5116,7 +5116,7 @@
         <v>25</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
         <v>7.8</v>
@@ -5128,13 +5128,13 @@
         <v>32</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>38</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G19" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>4.8</v>
@@ -5193,7 +5193,7 @@
         <v>5.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
@@ -5205,37 +5205,37 @@
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U19" t="n">
         <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="X19" t="n">
         <v>36</v>
       </c>
       <c r="Y19" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="Z19" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AA19" t="n">
         <v>190</v>
@@ -5283,49 +5283,49 @@
         <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
       </c>
       <c r="AS19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>18</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>3.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>10.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="BE19" t="n">
         <v>4.3</v>
@@ -5334,71 +5334,71 @@
         <v>4.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>11.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>3.05</v>
       </c>
       <c r="H20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I20" t="n">
         <v>2.88</v>
@@ -5444,10 +5444,10 @@
         <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -5468,7 +5468,7 @@
         <v>1.94</v>
       </c>
       <c r="S20" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="T20" t="n">
         <v>1.37</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
         <v>4.4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
         <v>1.19</v>
@@ -5710,19 +5710,19 @@
         <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="T21" t="n">
         <v>1.37</v>
@@ -5731,10 +5731,10 @@
         <v>3.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
         <v>55</v>
@@ -5743,28 +5743,28 @@
         <v>32</v>
       </c>
       <c r="Z21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH21" t="n">
         <v>16.5</v>
@@ -5773,10 +5773,10 @@
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>22</v>
@@ -5791,122 +5791,122 @@
         <v>13.5</v>
       </c>
       <c r="AP21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>7</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AS21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AY21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF21" t="n">
-        <v>5.6</v>
+        <v>3.95</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH21" t="n">
         <v>6.4</v>
       </c>
       <c r="BI21" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BJ21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR21" t="n">
         <v>17.5</v>
       </c>
       <c r="BS21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ21" t="n">
         <v>9.6</v>
       </c>
       <c r="CA21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -5937,46 +5937,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
         <v>5.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.06</v>
       </c>
       <c r="P22" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R22" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T22" t="n">
         <v>1.28</v>
@@ -5985,10 +5985,10 @@
         <v>3.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
@@ -6000,7 +6000,7 @@
         <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
         <v>95</v>
@@ -6018,149 +6018,149 @@
         <v>36</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
         <v>19</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AM22" t="n">
         <v>32</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT22" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AU22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA22" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="BB22" t="n">
         <v>7</v>
       </c>
-      <c r="AS22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="n">
         <v>7.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BJ22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP22" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW22" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BX22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ22" t="n">
         <v>7.4</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6191,58 +6191,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H23" t="n">
         <v>2.74</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
         <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
         <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -6254,7 +6254,7 @@
         <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AB23" t="n">
         <v>12</v>
@@ -6284,73 +6284,73 @@
         <v>44</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT23" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS23" t="n">
+      <c r="AU23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6</v>
-      </c>
       <c r="BF23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>
@@ -6448,13 +6448,13 @@
         <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="I24" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>2.78</v>
@@ -6463,19 +6463,19 @@
         <v>3.15</v>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M24" t="n">
         <v>1.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O24" t="n">
         <v>1.63</v>
       </c>
       <c r="P24" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
         <v>2.92</v>
@@ -6493,10 +6493,10 @@
         <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
         <v>9</v>
@@ -6553,37 +6553,37 @@
         <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="AR24" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA24" t="n">
         <v>5</v>
@@ -6616,13 +6616,13 @@
         <v>12.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6640,7 +6640,7 @@
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT24" t="n">
         <v>5.1</v>
@@ -6649,7 +6649,7 @@
         <v>4.3</v>
       </c>
       <c r="BV24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
         <v>8.4</v>
@@ -6658,17 +6658,17 @@
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 00:23:10</t>
+          <t>2026-06-19 02:35:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,73 +857,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N2" t="n">
         <v>2.5</v>
       </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.68</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
         <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
@@ -932,103 +932,103 @@
         <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="n">
         <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AM2" t="n">
         <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
         <v>6.2</v>
       </c>
-      <c r="AS2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BE2" t="n">
         <v>130</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,47 +1040,47 @@
         <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.24</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>5.1</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.08</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.22</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -1135,10 +1135,10 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
         <v>1.6</v>
@@ -1153,16 +1153,16 @@
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
         <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1219,10 +1219,10 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>6.6</v>
@@ -1231,22 +1231,22 @@
         <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>6</v>
@@ -1255,10 +1255,10 @@
         <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
         <v>7</v>
@@ -1267,7 +1267,7 @@
         <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
         <v>7.6</v>
@@ -1318,10 +1318,10 @@
         <v>50</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
         <v>2.24</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -1365,100 +1365,100 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.5</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.74</v>
-      </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.4</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2.72</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.46</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y4" t="n">
         <v>9.6</v>
       </c>
-      <c r="Y4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
         <v>150</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
         <v>210</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AL4" t="n">
         <v>170</v>
@@ -1467,128 +1467,128 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
         <v>600</v>
       </c>
       <c r="AP4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AT4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BB4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK4" t="n">
         <v>6</v>
       </c>
-      <c r="AY4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G5" t="n">
         <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
         <v>30</v>
@@ -1685,13 +1685,13 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
@@ -1709,7 +1709,7 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
         <v>70</v>
@@ -1721,10 +1721,10 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AP5" t="n">
         <v>6.8</v>
@@ -1736,19 +1736,19 @@
         <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1757,10 +1757,10 @@
         <v>7.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
         <v>8.800000000000001</v>
@@ -1769,19 +1769,19 @@
         <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI5" t="n">
         <v>2.72</v>
@@ -1790,16 +1790,16 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
         <v>3.45</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>3.3</v>
       </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
         <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
         <v>5.1</v>
@@ -1888,7 +1888,7 @@
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.24</v>
@@ -1900,16 +1900,16 @@
         <v>7.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
         <v>2.1</v>
@@ -1918,7 +1918,7 @@
         <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V6" t="n">
         <v>1.24</v>
@@ -1975,7 +1975,7 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO6" t="n">
         <v>270</v>
@@ -1984,19 +1984,19 @@
         <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AR6" t="n">
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
         <v>13.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV6" t="n">
         <v>17.5</v>
@@ -2026,31 +2026,31 @@
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
         <v>22</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BJ6" t="n">
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN6" t="n">
         <v>5</v>
@@ -2062,31 +2062,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
         <v>2.02</v>
@@ -2139,19 +2139,19 @@
         <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
@@ -2166,13 +2166,13 @@
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.92</v>
@@ -2181,10 +2181,10 @@
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7" t="n">
         <v>13</v>
@@ -2196,19 +2196,19 @@
         <v>15.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
@@ -2220,7 +2220,7 @@
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AL7" t="n">
         <v>150</v>
@@ -2253,7 +2253,7 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>18.5</v>
@@ -2274,73 +2274,73 @@
         <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BD7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE7" t="n">
         <v>29</v>
       </c>
       <c r="BF7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG7" t="n">
         <v>13</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.81</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.75</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.76</v>
+        <v>9.6</v>
       </c>
       <c r="BT7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BX7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.74</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I8" t="n">
         <v>1.71</v>
@@ -2408,43 +2408,43 @@
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
         <v>2.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z8" t="n">
         <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB8" t="n">
         <v>22</v>
@@ -2453,7 +2453,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>17.5</v>
@@ -2462,7 +2462,7 @@
         <v>46</v>
       </c>
       <c r="AG8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -2477,134 +2477,134 @@
         <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AO8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU8" t="n">
         <v>8.6</v>
       </c>
-      <c r="AP8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
         <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.4</v>
+        <v>48</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>48</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.6</v>
+        <v>60</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.98</v>
+        <v>4.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="BN8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
         <v>46</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="BR8" t="n">
         <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
         <v>5.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.35</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2662,37 +2662,37 @@
         <v>3.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
         <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
         <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
         <v>13.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z9" t="n">
         <v>16</v>
@@ -2704,7 +2704,7 @@
         <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>12</v>
@@ -2734,10 +2734,10 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
         <v>24</v>
@@ -2749,7 +2749,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
         <v>14.5</v>
@@ -2761,25 +2761,25 @@
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY9" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC9" t="n">
         <v>32</v>
@@ -2788,13 +2788,13 @@
         <v>42</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -2913,7 +2913,7 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2928,13 +2928,13 @@
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
         <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>1.48</v>
@@ -2946,7 +2946,7 @@
         <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2958,7 +2958,7 @@
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
@@ -2991,22 +2991,22 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
         <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>5.8</v>
@@ -3015,37 +3015,37 @@
         <v>4.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BD10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE10" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BF10" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
         <v>6.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>16</v>
@@ -3158,52 +3158,52 @@
         <v>6.2</v>
       </c>
       <c r="K11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="T11" t="n">
         <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="Z11" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -3212,16 +3212,16 @@
         <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
         <v>120</v>
       </c>
       <c r="AE11" t="n">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
@@ -3230,40 +3230,40 @@
         <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK11" t="n">
         <v>15.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AM11" t="n">
         <v>270</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AO11" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>18</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>34</v>
-      </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU11" t="n">
         <v>11.5</v>
@@ -3272,40 +3272,40 @@
         <v>42</v>
       </c>
       <c r="AW11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG11" t="n">
         <v>10</v>
       </c>
-      <c r="AX11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>15</v>
-      </c>
       <c r="BH11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI11" t="n">
         <v>3.35</v>
@@ -3314,16 +3314,16 @@
         <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BO11" t="n">
         <v>3.15</v>
@@ -3338,35 +3338,35 @@
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BT11" t="n">
         <v>17</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
         <v>1.67</v>
@@ -3412,16 +3412,16 @@
         <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
@@ -3430,67 +3430,67 @@
         <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
         <v>700</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AF12" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
       </c>
       <c r="AJ12" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
         <v>95</v>
@@ -3499,118 +3499,118 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.92</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
         <v>5.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.09</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.09</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.09</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.09</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
         <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.1</v>
@@ -3672,31 +3672,31 @@
         <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
         <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.22</v>
@@ -3756,58 +3756,58 @@
         <v>11.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AS13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE13" t="n">
         <v>13</v>
       </c>
-      <c r="AT13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BF13" t="n">
         <v>10</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
         <v>12.5</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.4</v>
@@ -3837,22 +3837,22 @@
         <v>3.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.37</v>
@@ -3929,37 +3929,37 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>950</v>
@@ -3971,10 +3971,10 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC14" t="n">
         <v>14</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3983,10 +3983,10 @@
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
@@ -3995,10 +3995,10 @@
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
         <v>500</v>
@@ -4013,112 +4013,112 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.56</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.68</v>
+        <v>9.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.42</v>
+        <v>6.8</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.68</v>
+        <v>5.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.66</v>
+        <v>5.1</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
         <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.66</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.94</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.73</v>
+        <v>5.5</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="BT14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.67</v>
+        <v>4.6</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.89</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G15" t="n">
         <v>1.32</v>
@@ -4168,10 +4168,10 @@
         <v>12.5</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
         <v>6.8</v>
@@ -4180,7 +4180,7 @@
         <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
         <v>5.5</v>
@@ -4192,7 +4192,7 @@
         <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.59</v>
@@ -4201,10 +4201,10 @@
         <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
@@ -4240,7 +4240,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>32</v>
@@ -4267,58 +4267,58 @@
         <v>280</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>7</v>
       </c>
-      <c r="AR15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS15" t="n">
+      <c r="BA15" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BB15" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="n">
         <v>4.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>1.46</v>
       </c>
       <c r="G16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="K16" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.07</v>
@@ -4446,25 +4446,25 @@
         <v>4.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
         <v>1.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V16" t="n">
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4479,7 +4479,7 @@
         <v>160</v>
       </c>
       <c r="AB16" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
         <v>970</v>
@@ -4494,7 +4494,7 @@
         <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
         <v>970</v>
@@ -4518,55 +4518,55 @@
         <v>3.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AQ16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA16" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BB16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
         <v>3.1</v>
@@ -4578,37 +4578,37 @@
         <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="BN16" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
@@ -4620,23 +4620,23 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>2.56</v>
+        <v>4.3</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.52</v>
+        <v>6.6</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -4670,19 +4670,19 @@
         <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H17" t="n">
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.17</v>
@@ -4691,7 +4691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
         <v>1.08</v>
@@ -4709,16 +4709,16 @@
         <v>1.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>3.55</v>
       </c>
       <c r="V17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4730,16 +4730,16 @@
         <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
         <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
@@ -4748,16 +4748,16 @@
         <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK17" t="n">
         <v>500</v>
@@ -4766,131 +4766,131 @@
         <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.17</v>
+        <v>7.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.18</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.19</v>
+        <v>3.45</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.18</v>
+        <v>4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.17</v>
+        <v>5.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.19</v>
+        <v>6.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.18</v>
+        <v>6.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.19</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>3.65</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.19</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -4927,16 +4927,16 @@
         <v>1.99</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
         <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.35</v>
@@ -4945,28 +4945,28 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
         <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
         <v>1.31</v>
@@ -4975,7 +4975,7 @@
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4984,109 +4984,109 @@
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="n">
         <v>17</v>
       </c>
-      <c r="AE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AT18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU18" t="n">
         <v>8</v>
       </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX18" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AY18" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH18" t="n">
         <v>4</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ18" t="n">
         <v>9.6</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.26</v>
@@ -5199,34 +5199,34 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
         <v>1.51</v>
       </c>
       <c r="R19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T19" t="n">
         <v>1.7</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.66</v>
-      </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V19" t="n">
         <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="X19" t="n">
         <v>36</v>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
         <v>32</v>
@@ -5253,19 +5253,19 @@
         <v>480</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>390</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AK19" t="n">
         <v>18</v>
@@ -5277,64 +5277,64 @@
         <v>320</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AO19" t="n">
         <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="n">
         <v>4.7</v>
@@ -5346,13 +5346,13 @@
         <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
@@ -5364,41 +5364,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
         <v>19</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT19" t="n">
         <v>10.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV19" t="n">
         <v>65</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BZ19" t="n">
         <v>11.5</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -5429,58 +5429,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I20" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>1.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Q20" t="n">
         <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="S20" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="T20" t="n">
         <v>1.37</v>
       </c>
       <c r="U20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="X20" t="n">
         <v>950</v>
@@ -5492,13 +5492,13 @@
         <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>950</v>
       </c>
       <c r="AC20" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
         <v>970</v>
@@ -5537,88 +5537,88 @@
         <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.96</v>
+        <v>2.58</v>
       </c>
       <c r="BF20" t="n">
         <v>2.94</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.72</v>
+        <v>5.1</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
@@ -5630,29 +5630,29 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.72</v>
+        <v>5</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>4.4</v>
@@ -5707,40 +5707,40 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="T21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.37</v>
       </c>
-      <c r="U21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.41</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Y21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
         <v>36</v>
@@ -5749,10 +5749,10 @@
         <v>130</v>
       </c>
       <c r="AB21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD21" t="n">
         <v>19</v>
@@ -5761,22 +5761,22 @@
         <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
         <v>16.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
         <v>22</v>
@@ -5785,128 +5785,128 @@
         <v>38</v>
       </c>
       <c r="AN21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV21" t="n">
         <v>6.6</v>
       </c>
-      <c r="AO21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA21" t="n">
         <v>7.6</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="BB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD21" t="n">
         <v>7</v>
       </c>
-      <c r="AR21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BJ21" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BQ21" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS21" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV21" t="n">
         <v>22</v>
       </c>
       <c r="BW21" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX21" t="n">
         <v>23</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
         <v>9.6</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -5940,19 +5940,19 @@
         <v>1.89</v>
       </c>
       <c r="G22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.14</v>
@@ -5967,10 +5967,10 @@
         <v>1.06</v>
       </c>
       <c r="P22" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R22" t="n">
         <v>2.62</v>
@@ -5979,16 +5979,16 @@
         <v>1.54</v>
       </c>
       <c r="T22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="U22" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="V22" t="n">
         <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X22" t="n">
         <v>950</v>
@@ -6000,16 +6000,16 @@
         <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AE22" t="n">
         <v>500</v>
@@ -6027,16 +6027,16 @@
         <v>500</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
         <v>970</v>
       </c>
       <c r="AM22" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>4.8</v>
@@ -6045,64 +6045,64 @@
         <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW22" t="n">
         <v>7.6</v>
       </c>
-      <c r="AR22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT22" t="n">
+      <c r="AX22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA22" t="n">
         <v>7.2</v>
       </c>
-      <c r="AU22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH22" t="n">
         <v>7.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.199999999999999</v>
@@ -6114,19 +6114,19 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN22" t="n">
         <v>6.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR22" t="n">
         <v>14.5</v>
@@ -6135,10 +6135,10 @@
         <v>6.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV22" t="n">
         <v>21</v>
@@ -6153,14 +6153,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -6191,88 +6191,88 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
         <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -6296,125 +6296,125 @@
         <v>40</v>
       </c>
       <c r="AO23" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.64</v>
@@ -6475,7 +6475,7 @@
         <v>1.63</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q24" t="n">
         <v>2.92</v>
@@ -6487,16 +6487,16 @@
         <v>6.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V24" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
         <v>9</v>
@@ -6508,10 +6508,10 @@
         <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AC24" t="n">
         <v>7.2</v>
@@ -6523,10 +6523,10 @@
         <v>500</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>32</v>
@@ -6553,58 +6553,58 @@
         <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="n">
         <v>2.54</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 02:35:44</t>
+          <t>2026-06-19 04:48:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.25</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
         <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
         <v>8.4</v>
       </c>
       <c r="Y2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP2" t="n">
         <v>7.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="BC2" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
         <v>12</v>
       </c>
       <c r="BK2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>170</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BO2" t="n">
         <v>6.2</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>150</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT2" t="n">
         <v>4.5</v>
       </c>
-      <c r="BP2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS2" t="n">
+      <c r="BU2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BT2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>10</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
         <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
         <v>2.12</v>
@@ -1123,10 +1123,10 @@
         <v>5.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -1135,13 +1135,13 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q3" t="n">
         <v>2.34</v>
@@ -1150,13 +1150,13 @@
         <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
         <v>1.23</v>
@@ -1168,10 +1168,10 @@
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
@@ -1180,7 +1180,7 @@
         <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1195,7 +1195,7 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
         <v>240</v>
@@ -1219,16 +1219,16 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -1237,22 +1237,22 @@
         <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
         <v>9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1261,28 +1261,28 @@
         <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE3" t="n">
         <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="n">
         <v>3.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,47 +1294,47 @@
         <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR3" t="n">
         <v>38</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BZ3" t="n">
         <v>38</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1365,91 +1365,91 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
         <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
         <v>210</v>
@@ -1458,43 +1458,43 @@
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>11.5</v>
@@ -1503,92 +1503,92 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP4" t="n">
         <v>23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
         <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
         <v>6.6</v>
@@ -1634,76 +1634,76 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
         <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
         <v>9</v>
       </c>
       <c r="AH5" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
@@ -1712,46 +1712,46 @@
         <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>7.2</v>
@@ -1760,89 +1760,89 @@
         <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>120</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.42</v>
+        <v>140</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="H6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I6" t="n">
         <v>4.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.1</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M6" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="T6" t="n">
         <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -1939,13 +1939,13 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
         <v>60</v>
@@ -1954,19 +1954,19 @@
         <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
         <v>32</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1975,10 +1975,10 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AO6" t="n">
-        <v>270</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -1990,7 +1990,7 @@
         <v>20</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
         <v>13.5</v>
@@ -1999,40 +1999,40 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
         <v>20</v>
       </c>
       <c r="BB6" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
         <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>5.2</v>
@@ -2041,19 +2041,19 @@
         <v>4.7</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="BN6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO6" t="n">
         <v>4.5</v>
@@ -2062,31 +2062,31 @@
         <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT6" t="n">
         <v>8.6</v>
       </c>
-      <c r="BT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2130,34 +2130,34 @@
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
         <v>2.02</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
@@ -2169,19 +2169,19 @@
         <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W7" t="n">
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
         <v>8.800000000000001</v>
@@ -2205,10 +2205,10 @@
         <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
@@ -2250,13 +2250,13 @@
         <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -2280,7 +2280,7 @@
         <v>50</v>
       </c>
       <c r="BE7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BF7" t="n">
         <v>46</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I8" t="n">
         <v>1.71</v>
@@ -2399,22 +2399,22 @@
         <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
         <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -2432,7 +2432,7 @@
         <v>2.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>19</v>
@@ -2453,7 +2453,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE8" t="n">
         <v>17.5</v>
@@ -2483,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO8" t="n">
         <v>8.800000000000001</v>
@@ -2492,10 +2492,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
         <v>13.5</v>
@@ -2510,7 +2510,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>26</v>
@@ -2525,7 +2525,7 @@
         <v>25</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
         <v>48</v>
@@ -2543,7 +2543,7 @@
         <v>7.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
         <v>2.52</v>
@@ -2558,25 +2558,25 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BN8" t="n">
         <v>9</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
         <v>46</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR8" t="n">
         <v>50</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
         <v>5.8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
         <v>3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
@@ -2668,13 +2668,13 @@
         <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
         <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
         <v>1.83</v>
@@ -2683,19 +2683,19 @@
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W9" t="n">
         <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
         <v>9.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA9" t="n">
         <v>34</v>
@@ -2707,19 +2707,19 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
         <v>44</v>
@@ -2731,10 +2731,10 @@
         <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
         <v>44</v>
@@ -2743,58 +2743,58 @@
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="BC9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD9" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I10" t="n">
         <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.43</v>
@@ -2919,7 +2919,7 @@
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
         <v>2.02</v>
@@ -2928,7 +2928,7 @@
         <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.81</v>
@@ -2937,142 +2937,142 @@
         <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK10" t="n">
         <v>32</v>
       </c>
-      <c r="Y10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>500</v>
-      </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7</v>
       </c>
-      <c r="AR10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AV10" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.54</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
@@ -3090,7 +3090,7 @@
         <v>6.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
         <v>6.2</v>
@@ -3167,25 +3167,25 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
         <v>1.71</v>
@@ -3194,13 +3194,13 @@
         <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>140</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>170</v>
@@ -3218,7 +3218,7 @@
         <v>120</v>
       </c>
       <c r="AE11" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -3236,7 +3236,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
         <v>48</v>
@@ -3245,22 +3245,22 @@
         <v>270</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>7.6</v>
@@ -3272,10 +3272,10 @@
         <v>42</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY11" t="n">
         <v>6.6</v>
@@ -3284,7 +3284,7 @@
         <v>30</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
         <v>8.6</v>
@@ -3296,13 +3296,13 @@
         <v>38</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="n">
         <v>4.1</v>
@@ -3314,13 +3314,13 @@
         <v>19</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN11" t="n">
         <v>3.65</v>
@@ -3329,7 +3329,7 @@
         <v>3.15</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ11" t="n">
         <v>6</v>
@@ -3338,35 +3338,35 @@
         <v>36</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT11" t="n">
         <v>17</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="CA11" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>5.3</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>6.6</v>
@@ -3427,16 +3427,16 @@
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
         <v>1.82</v>
@@ -3448,10 +3448,10 @@
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
         <v>23</v>
@@ -3481,7 +3481,7 @@
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>700</v>
@@ -3505,55 +3505,55 @@
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AX12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AY12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
         <v>9</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3657,10 +3657,10 @@
         <v>1.82</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.85</v>
@@ -3672,25 +3672,25 @@
         <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
         <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.83</v>
@@ -3720,16 +3720,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
         <v>9.800000000000001</v>
@@ -3738,7 +3738,7 @@
         <v>60</v>
       </c>
       <c r="AI13" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -3768,10 +3768,10 @@
         <v>32</v>
       </c>
       <c r="AS13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
@@ -3780,13 +3780,13 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
         <v>16.5</v>
@@ -3804,13 +3804,13 @@
         <v>27</v>
       </c>
       <c r="BE13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF13" t="n">
         <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="n">
         <v>3.5</v>
@@ -3822,7 +3822,7 @@
         <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3846,13 +3846,13 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13" t="n">
         <v>8.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3864,7 +3864,7 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -3911,16 +3911,16 @@
         <v>1.77</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.37</v>
@@ -3935,34 +3935,34 @@
         <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
         <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
         <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3971,10 +3971,10 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -3983,19 +3983,19 @@
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
         <v>65</v>
@@ -4013,13 +4013,13 @@
         <v>700</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
         <v>9.4</v>
@@ -4028,13 +4028,13 @@
         <v>5.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>5.6</v>
@@ -4043,28 +4043,28 @@
         <v>5.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH14" t="n">
         <v>3.85</v>
@@ -4076,13 +4076,13 @@
         <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN14" t="n">
         <v>4.7</v>
@@ -4094,31 +4094,31 @@
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
         <v>8</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="H15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -4192,40 +4192,40 @@
         <v>2.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
         <v>1.59</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
         <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="X15" t="n">
         <v>70</v>
       </c>
       <c r="Y15" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>540</v>
       </c>
       <c r="AA15" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
         <v>14.5</v>
@@ -4240,10 +4240,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AI15" t="n">
         <v>460</v>
@@ -4255,7 +4255,7 @@
         <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AM15" t="n">
         <v>180</v>
@@ -4270,58 +4270,58 @@
         <v>21</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT15" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
         <v>11.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.6</v>
+        <v>16.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY15" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
         <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG15" t="n">
         <v>15</v>
       </c>
       <c r="BH15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI15" t="n">
         <v>3.45</v>
@@ -4330,13 +4330,13 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
         <v>3.95</v>
@@ -4348,41 +4348,41 @@
         <v>7.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR15" t="n">
         <v>23</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>11.5</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4431,40 +4431,40 @@
         <v>6.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>1.07</v>
       </c>
       <c r="P16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S16" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T16" t="n">
         <v>1.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X16" t="n">
         <v>950</v>
@@ -4473,7 +4473,7 @@
         <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="n">
         <v>160</v>
@@ -4512,73 +4512,73 @@
         <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AO16" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT16" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE16" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
         <v>3.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BI16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ16" t="n">
         <v>1000</v>
@@ -4590,10 +4590,10 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.59</v>
+        <v>2.88</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO16" t="n">
         <v>4.2</v>
@@ -4602,7 +4602,7 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4614,29 +4614,29 @@
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
         <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
         <v>2.34</v>
       </c>
       <c r="I17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
         <v>5.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
@@ -4697,28 +4697,28 @@
         <v>1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="U17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="V17" t="n">
         <v>1.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
         <v>950</v>
@@ -4775,61 +4775,61 @@
         <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AZ17" t="n">
         <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
         <v>5.8</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BI17" t="n">
         <v>5.2</v>
@@ -4838,13 +4838,13 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
@@ -4862,7 +4862,7 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
@@ -4874,7 +4874,7 @@
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -4945,19 +4945,19 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
         <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
         <v>2.96</v>
@@ -4966,7 +4966,7 @@
         <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
         <v>1.31</v>
@@ -4975,7 +4975,7 @@
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
         <v>21</v>
@@ -4984,7 +4984,7 @@
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
@@ -5005,7 +5005,7 @@
         <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI18" t="n">
         <v>48</v>
@@ -5029,7 +5029,7 @@
         <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -5044,7 +5044,7 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>14.5</v>
@@ -5059,7 +5059,7 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
         <v>40</v>
@@ -5074,10 +5074,10 @@
         <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
         <v>34</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
         <v>1.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
         <v>1.51</v>
@@ -5214,25 +5214,25 @@
         <v>1.71</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
         <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
         <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="Y19" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z19" t="n">
         <v>420</v>
@@ -5253,13 +5253,13 @@
         <v>480</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
         <v>390</v>
@@ -5283,16 +5283,16 @@
         <v>200</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
@@ -5304,7 +5304,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -5328,7 +5328,7 @@
         <v>14.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
         <v>4.7</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>2.46</v>
       </c>
       <c r="G20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H20" t="n">
         <v>2.36</v>
       </c>
       <c r="I20" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J20" t="n">
         <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.2</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R20" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="T20" t="n">
         <v>1.37</v>
@@ -5477,7 +5477,7 @@
         <v>3.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
         <v>1.56</v>
@@ -5537,112 +5537,112 @@
         <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AQ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR20" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AS20" t="n">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.54</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>5.9</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.48</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="BF20" t="n">
         <v>2.94</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.05</v>
+        <v>1.49</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU20" t="n">
         <v>5.1</v>
       </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>5</v>
-      </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G21" t="n">
         <v>2.04</v>
@@ -5695,7 +5695,7 @@
         <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
@@ -5707,28 +5707,28 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R21" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="T21" t="n">
         <v>1.4</v>
       </c>
       <c r="U21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
@@ -5743,13 +5743,13 @@
         <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="AA21" t="n">
         <v>130</v>
       </c>
       <c r="AB21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC21" t="n">
         <v>13.5</v>
@@ -5785,7 +5785,7 @@
         <v>38</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO21" t="n">
         <v>15.5</v>
@@ -5794,28 +5794,28 @@
         <v>8.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU21" t="n">
         <v>10.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
         <v>6.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
         <v>6.2</v>
@@ -5854,7 +5854,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5866,22 +5866,22 @@
         <v>5.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP21" t="n">
         <v>12</v>
       </c>
       <c r="BQ21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR21" t="n">
         <v>17</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU21" t="n">
         <v>5.2</v>
@@ -5890,7 +5890,7 @@
         <v>22</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX21" t="n">
         <v>23</v>
@@ -5899,14 +5899,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BZ21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -5970,19 +5970,19 @@
         <v>5.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R22" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="S22" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="T22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="U22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
         <v>1.38</v>
@@ -6006,7 +6006,7 @@
         <v>950</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AD22" t="n">
         <v>40</v>
@@ -6039,34 +6039,34 @@
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO22" t="n">
         <v>12</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AR22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -6078,10 +6078,10 @@
         <v>10.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB22" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -6090,77 +6090,77 @@
         <v>13.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="n">
         <v>7.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BJ22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN22" t="n">
         <v>6.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR22" t="n">
         <v>14.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT22" t="n">
         <v>9</v>
       </c>
       <c r="BU22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV22" t="n">
         <v>21</v>
       </c>
       <c r="BW22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
         <v>3.4</v>
@@ -6209,55 +6209,55 @@
         <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="V23" t="n">
         <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z23" t="n">
         <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>7.8</v>
@@ -6266,25 +6266,25 @@
         <v>13</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK23" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="n">
         <v>120</v>
@@ -6293,73 +6293,73 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO23" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW23" t="n">
         <v>13.5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BC23" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH23" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="BJ23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK23" t="n">
         <v>6.4</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN23" t="n">
         <v>5.7</v>
@@ -6377,16 +6377,16 @@
         <v>4.3</v>
       </c>
       <c r="BP23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BQ23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT23" t="n">
         <v>5.9</v>
@@ -6395,10 +6395,10 @@
         <v>4.4</v>
       </c>
       <c r="BV23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
@@ -6407,14 +6407,14 @@
         <v>11.5</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA23" t="n">
         <v>11</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>
@@ -6445,61 +6445,61 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
         <v>3.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J24" t="n">
         <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L24" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="M24" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N24" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="P24" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="U24" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="Y24" t="n">
         <v>8.199999999999999</v>
@@ -6508,10 +6508,10 @@
         <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC24" t="n">
         <v>7.2</v>
@@ -6553,19 +6553,19 @@
         <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>13</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AU24" t="n">
         <v>6</v>
@@ -6574,7 +6574,7 @@
         <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>18.5</v>
@@ -6583,46 +6583,46 @@
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH24" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="BI24" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="BJ24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6634,41 +6634,41 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BT24" t="n">
         <v>5.1</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW24" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-19 04:48:46</t>
+          <t>2026-06-19 07:01:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -863,145 +863,145 @@
         <v>1.75</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
         <v>2.32</v>
       </c>
       <c r="X2" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
         <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AF2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>16</v>
-      </c>
       <c r="AL2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
         <v>5.5</v>
       </c>
       <c r="AO2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP2" t="n">
         <v>34</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16</v>
       </c>
       <c r="AU2" t="n">
         <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -1010,16 +1010,16 @@
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
         <v>5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BI2" t="n">
         <v>4.9</v>
@@ -1028,49 +1028,49 @@
         <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP2" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BS2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
         <v>8.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I3" t="n">
         <v>1.79</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
@@ -1132,31 +1132,31 @@
         <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>2.26</v>
@@ -1168,13 +1168,13 @@
         <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
         <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
         <v>19.5</v>
@@ -1186,13 +1186,13 @@
         <v>9.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF3" t="n">
         <v>40</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
         <v>18.5</v>
@@ -1204,7 +1204,7 @@
         <v>120</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
@@ -1216,10 +1216,10 @@
         <v>65</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.199999999999999</v>
@@ -1261,13 +1261,13 @@
         <v>50</v>
       </c>
       <c r="BD3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE3" t="n">
         <v>70</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BG3" t="n">
         <v>9</v>
@@ -1276,40 +1276,40 @@
         <v>3.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BN3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>46</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU3" t="n">
         <v>4.1</v>
@@ -1324,17 +1324,17 @@
         <v>32</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3" t="n">
         <v>19.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1371,46 +1371,46 @@
         <v>1.26</v>
       </c>
       <c r="H4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>6.8</v>
       </c>
       <c r="K4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
         <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
         <v>1.06</v>
@@ -1419,7 +1419,7 @@
         <v>4.8</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y4" t="n">
         <v>100</v>
@@ -1428,22 +1428,22 @@
         <v>170</v>
       </c>
       <c r="AA4" t="n">
-        <v>850</v>
+        <v>930</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
         <v>60</v>
       </c>
       <c r="AE4" t="n">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1452,7 +1452,7 @@
         <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ4" t="n">
         <v>8.800000000000001</v>
@@ -1467,25 +1467,25 @@
         <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AP4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
         <v>13.5</v>
@@ -1497,25 +1497,25 @@
         <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>34</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
         <v>150</v>
@@ -1524,19 +1524,19 @@
         <v>4.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4" t="n">
         <v>14.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>190</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
         <v>18</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BZ4" t="n">
         <v>11.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         <v>3.3</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.46</v>
@@ -1655,22 +1655,22 @@
         <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
@@ -1688,13 +1688,13 @@
         <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>11.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF5" t="n">
         <v>23</v>
@@ -1724,7 +1724,7 @@
         <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP5" t="n">
         <v>11</v>
@@ -1781,13 +1781,13 @@
         <v>21</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
         <v>7.6</v>
@@ -1799,40 +1799,40 @@
         <v>100</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>19.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
         <v>36</v>
       </c>
       <c r="BY5" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -1879,19 +1879,19 @@
         <v>2.96</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1918,7 +1918,7 @@
         <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
         <v>1.57</v>
@@ -1927,13 +1927,13 @@
         <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA6" t="n">
         <v>280</v>
@@ -1951,22 +1951,22 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>65</v>
@@ -1978,16 +1978,16 @@
         <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
         <v>20</v>
@@ -1999,7 +1999,7 @@
         <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
         <v>26</v>
@@ -2011,25 +2011,25 @@
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD6" t="n">
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BF6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG6" t="n">
         <v>21</v>
@@ -2041,16 +2041,16 @@
         <v>2.68</v>
       </c>
       <c r="BJ6" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BN6" t="n">
         <v>6.2</v>
@@ -2059,16 +2059,16 @@
         <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
         <v>5.9</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
         <v>4.1</v>
@@ -2151,10 +2151,10 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
         <v>1.89</v>
@@ -2163,13 +2163,13 @@
         <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
         <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
         <v>2.08</v>
@@ -2184,16 +2184,16 @@
         <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -2202,61 +2202,61 @@
         <v>10.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>40</v>
       </c>
       <c r="AJ7" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>500</v>
+        <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR7" t="n">
         <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU7" t="n">
         <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>25</v>
@@ -2265,16 +2265,16 @@
         <v>15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
         <v>34</v>
       </c>
       <c r="BB7" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="BC7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD7" t="n">
         <v>50</v>
@@ -2286,19 +2286,19 @@
         <v>48</v>
       </c>
       <c r="BG7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,37 +2310,37 @@
         <v>7.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7" t="n">
         <v>4.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
         <v>16</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>32</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
         <v>1.66</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
         <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2414,19 +2414,19 @@
         <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
         <v>1.18</v>
@@ -2435,7 +2435,7 @@
         <v>2.5</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
         <v>23</v>
@@ -2444,7 +2444,7 @@
         <v>85</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
         <v>10</v>
@@ -2453,13 +2453,13 @@
         <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
         <v>9.199999999999999</v>
@@ -2468,133 +2468,133 @@
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AJ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH8" t="n">
         <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP8" t="n">
         <v>11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2659,7 +2659,7 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.31</v>
@@ -2668,52 +2668,52 @@
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R9" t="n">
         <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="X9" t="n">
         <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
         <v>9.4</v>
@@ -2725,121 +2725,121 @@
         <v>170</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="BB9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="n">
         <v>16</v>
       </c>
-      <c r="BC9" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BD9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
         <v>55</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BW9" t="n">
         <v>11.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -2889,73 +2889,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.16</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
         <v>40</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -2967,7 +2967,7 @@
         <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>9.199999999999999</v>
@@ -2979,55 +2979,55 @@
         <v>70</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
       </c>
       <c r="AM10" t="n">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
       </c>
       <c r="AQ10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
         <v>18.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18</v>
-      </c>
       <c r="AW10" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
         <v>30</v>
@@ -3036,7 +3036,7 @@
         <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD10" t="n">
         <v>27</v>
@@ -3045,16 +3045,16 @@
         <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3066,10 +3066,10 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO10" t="n">
         <v>3.6</v>
@@ -3078,22 +3078,22 @@
         <v>12</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW10" t="n">
         <v>8</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="n">
         <v>14.5</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
         <v>1.29</v>
@@ -3167,40 +3167,40 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
         <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X11" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="Z11" t="n">
         <v>540</v>
@@ -3212,97 +3212,97 @@
         <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AE11" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AF11" t="n">
         <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
         <v>460</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL11" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
         <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AT11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AX11" t="n">
         <v>7.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BF11" t="n">
         <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4.6</v>
@@ -3320,10 +3320,10 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO11" t="n">
         <v>3.4</v>
@@ -3332,7 +3332,7 @@
         <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BR11" t="n">
         <v>23</v>
@@ -3341,7 +3341,7 @@
         <v>7.4</v>
       </c>
       <c r="BT11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
         <v>6.2</v>
@@ -3350,23 +3350,23 @@
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BX11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="BZ11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="H12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J12" t="n">
         <v>5.6</v>
       </c>
-      <c r="I12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.5</v>
-      </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.15</v>
@@ -3424,7 +3424,7 @@
         <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P12" t="n">
         <v>5.1</v>
@@ -3433,22 +3433,22 @@
         <v>1.22</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="S12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -3457,25 +3457,25 @@
         <v>950</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB12" t="n">
         <v>950</v>
       </c>
       <c r="AC12" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AE12" t="n">
         <v>160</v>
       </c>
       <c r="AF12" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
@@ -3487,140 +3487,140 @@
         <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AK12" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AL12" t="n">
         <v>500</v>
       </c>
       <c r="AM12" t="n">
-        <v>46</v>
+        <v>790</v>
       </c>
       <c r="AN12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>25</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC12" t="n">
         <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>9</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>7</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CA12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3654,13 +3654,13 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
         <v>2.42</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J13" t="n">
         <v>4.3</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
         <v>1.08</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q13" t="n">
         <v>1.26</v>
       </c>
       <c r="R13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T13" t="n">
         <v>1.31</v>
@@ -3699,10 +3699,10 @@
         <v>3.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3732,10 +3732,10 @@
         <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="AI13" t="n">
         <v>500</v>
@@ -3750,7 +3750,7 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
         <v>55</v>
@@ -3759,19 +3759,19 @@
         <v>7.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="AR13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AT13" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU13" t="n">
         <v>12</v>
@@ -3783,37 +3783,37 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
         <v>6.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI13" t="n">
         <v>5.2</v>
@@ -3822,7 +3822,7 @@
         <v>8.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3846,13 +3846,13 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT13" t="n">
         <v>7.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3867,14 +3867,14 @@
         <v>6.6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.98</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.99</v>
-      </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>4.2</v>
@@ -3929,43 +3929,43 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V14" t="n">
         <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
         <v>150</v>
@@ -3977,10 +3977,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
         <v>13.5</v>
@@ -4004,19 +4004,19 @@
         <v>30</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP14" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>29</v>
@@ -4025,7 +4025,7 @@
         <v>70</v>
       </c>
       <c r="AT14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
         <v>8.4</v>
@@ -4034,13 +4034,13 @@
         <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX14" t="n">
         <v>12.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
         <v>15</v>
@@ -4064,25 +4064,25 @@
         <v>9.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH14" t="n">
         <v>4.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
@@ -4094,31 +4094,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT14" t="n">
         <v>7.8</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.25</v>
@@ -4183,28 +4183,28 @@
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="S15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
         <v>1.17</v>
@@ -4216,173 +4216,173 @@
         <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Z15" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA15" t="n">
         <v>180</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AE15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
       </c>
       <c r="AM15" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX15" t="n">
         <v>11</v>
       </c>
-      <c r="AU15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB15" t="n">
         <v>13.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
         <v>42</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4419,19 +4419,19 @@
         <v>2.66</v>
       </c>
       <c r="H16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -4449,16 +4449,16 @@
         <v>1.35</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -4473,19 +4473,19 @@
         <v>950</v>
       </c>
       <c r="Z16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA16" t="n">
         <v>500</v>
       </c>
-      <c r="AA16" t="n">
-        <v>900</v>
-      </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -4497,13 +4497,13 @@
         <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
         <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
         <v>500</v>
@@ -4515,34 +4515,34 @@
         <v>580</v>
       </c>
       <c r="AN16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO16" t="n">
         <v>9.4</v>
       </c>
-      <c r="AO16" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AP16" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX16" t="n">
         <v>7.8</v>
@@ -4554,19 +4554,19 @@
         <v>11.5</v>
       </c>
       <c r="BA16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB16" t="n">
         <v>11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>8</v>
@@ -4584,7 +4584,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4626,17 +4626,17 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16" t="n">
         <v>10.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4667,230 +4667,230 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="M17" t="n">
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="O17" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="T17" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="U17" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X17" t="n">
         <v>130</v>
       </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA17" t="n">
         <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD17" t="n">
         <v>19</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
         <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BJ17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP17" t="n">
         <v>12</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="BT17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU17" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="BV17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="BX17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="BZ17" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA17" t="n">
-        <v>5.4</v>
+        <v>2.98</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>5.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -4951,13 +4951,13 @@
         <v>1.06</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q18" t="n">
         <v>1.21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="S18" t="n">
         <v>1.52</v>
@@ -4966,7 +4966,7 @@
         <v>1.27</v>
       </c>
       <c r="U18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
@@ -4981,7 +4981,7 @@
         <v>950</v>
       </c>
       <c r="Z18" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA18" t="n">
         <v>500</v>
@@ -5020,28 +5020,28 @@
         <v>970</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO18" t="n">
         <v>12</v>
       </c>
       <c r="AP18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AS18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT18" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>6.6</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -5050,7 +5050,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -5065,7 +5065,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>16</v>
@@ -5080,10 +5080,10 @@
         <v>4.1</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI18" t="n">
         <v>5.1</v>
@@ -5092,59 +5092,59 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>6.8</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP18" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR18" t="n">
         <v>14.5</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT18" t="n">
         <v>9</v>
       </c>
       <c r="BU18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV18" t="n">
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ18" t="n">
         <v>6.8</v>
       </c>
       <c r="CA18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5175,61 +5175,61 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G19" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -5238,13 +5238,13 @@
         <v>19</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
         <v>13</v>
@@ -5259,31 +5259,31 @@
         <v>12.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK19" t="n">
         <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.199999999999999</v>
@@ -5292,7 +5292,7 @@
         <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>8.800000000000001</v>
@@ -5304,7 +5304,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
         <v>15.5</v>
@@ -5313,37 +5313,37 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
         <v>16.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
         <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
         <v>9.6</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="BJ19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
         <v>6</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN19" t="n">
         <v>5.7</v>
@@ -5364,41 +5364,41 @@
         <v>23</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT19" t="n">
         <v>5.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
         <v>3.85</v>
@@ -5444,7 +5444,7 @@
         <v>2.76</v>
       </c>
       <c r="K20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="L20" t="n">
         <v>1.74</v>
@@ -5456,22 +5456,22 @@
         <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="P20" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.58</v>
@@ -5483,7 +5483,7 @@
         <v>1.35</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" t="n">
         <v>8.4</v>
@@ -5501,7 +5501,7 @@
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
@@ -5513,7 +5513,7 @@
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -5537,10 +5537,10 @@
         <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR20" t="n">
         <v>13</v>
@@ -5549,13 +5549,13 @@
         <v>6</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU20" t="n">
         <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>6</v>
@@ -5564,10 +5564,10 @@
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
         <v>6.4</v>
@@ -5588,7 +5588,7 @@
         <v>6.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH20" t="n">
         <v>2.4</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN20" t="n">
         <v>7.2</v>
@@ -5618,13 +5618,13 @@
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT20" t="n">
         <v>5.1</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-19 11:30:49</t>
+          <t>2026-06-19 13:46:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Icelandic 2 Deild</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Throttur Vogar</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kari</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -926,22 +926,22 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -950,10 +950,10 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -962,62 +962,62 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>220</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>220</v>
+        <v>14.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>28</v>
+        <v>2.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>85</v>
+        <v>4.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>85</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>220</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>170</v>
+      </c>
+      <c r="BG2" t="n">
         <v>50</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>220</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
@@ -1080,515 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-19 18:18:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Miramar Misiones</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Huracan del Paso</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>190</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>46</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>960</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>110</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-19 18:18:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CA Ituzaingo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CSD Liniers de Ciudad Evita</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-19 18:18:24</t>
+          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CA Ituzaingo</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CSD Liniers de Ciudad Evita</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>44</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>150</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>170</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-19 20:34:23</t>
         </is>
       </c>
     </row>
